--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/7_eight_bus_radial_grid_1ph_ynyn_MP_pf_sc_results_6_bus.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/7_eight_bus_radial_grid_1ph_ynyn_MP_pf_sc_results_6_bus.xlsx
@@ -827,19 +827,19 @@
         <v>1.052070638302227</v>
       </c>
       <c r="O2">
-        <v>0.8416889876475661</v>
+        <v>0.8416889876475663</v>
       </c>
       <c r="P2">
-        <v>1.030712193904243</v>
+        <v>1.030712193904244</v>
       </c>
       <c r="Q2">
-        <v>23.56952022197289</v>
+        <v>23.56952022197288</v>
       </c>
       <c r="R2">
-        <v>-91.58959683084082</v>
+        <v>-91.58959683084075</v>
       </c>
       <c r="S2">
-        <v>155.9114873402058</v>
+        <v>155.9114873402059</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -886,16 +886,16 @@
         <v>1.033362770996141</v>
       </c>
       <c r="O3">
-        <v>0.8013810488011152</v>
+        <v>0.8013810488011154</v>
       </c>
       <c r="P3">
-        <v>1.03357014995835</v>
+        <v>1.033570149958351</v>
       </c>
       <c r="Q3">
-        <v>22.814816357365</v>
+        <v>22.81481635736498</v>
       </c>
       <c r="R3">
-        <v>-89.98391499028135</v>
+        <v>-89.98391499028126</v>
       </c>
       <c r="S3">
         <v>157.190019535551</v>
@@ -945,16 +945,16 @@
         <v>1.033362770995434</v>
       </c>
       <c r="O4">
-        <v>0.8013810488221487</v>
+        <v>0.8013810488221489</v>
       </c>
       <c r="P4">
-        <v>1.033570149967211</v>
+        <v>1.033570149967212</v>
       </c>
       <c r="Q4">
-        <v>22.81481635801401</v>
+        <v>22.814816358014</v>
       </c>
       <c r="R4">
-        <v>-89.98391498953956</v>
+        <v>-89.98391498953947</v>
       </c>
       <c r="S4">
         <v>157.1900195351253</v>
@@ -1001,19 +1001,19 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9925966232566392</v>
+        <v>0.9925966232566397</v>
       </c>
       <c r="O5">
-        <v>0.7534627028500445</v>
+        <v>0.7534627028500447</v>
       </c>
       <c r="P5">
-        <v>1.055274866785676</v>
+        <v>1.055274866785678</v>
       </c>
       <c r="Q5">
-        <v>22.21115328383782</v>
+        <v>22.2111532838378</v>
       </c>
       <c r="R5">
-        <v>-84.87011703381381</v>
+        <v>-84.87011703381374</v>
       </c>
       <c r="S5">
         <v>159.1717166617352</v>
@@ -1063,16 +1063,16 @@
         <v>1.033362770995434</v>
       </c>
       <c r="O6">
-        <v>0.8013810488221487</v>
+        <v>0.8013810488221488</v>
       </c>
       <c r="P6">
-        <v>1.033570149967211</v>
+        <v>1.033570149967212</v>
       </c>
       <c r="Q6">
-        <v>22.81481635801401</v>
+        <v>22.81481635801399</v>
       </c>
       <c r="R6">
-        <v>-89.98391498953956</v>
+        <v>-89.98391498953949</v>
       </c>
       <c r="S6">
         <v>157.1900195351253</v>
@@ -1122,16 +1122,16 @@
         <v>1.03336277094941</v>
       </c>
       <c r="O7">
-        <v>0.8013810488327402</v>
+        <v>0.8013810488327404</v>
       </c>
       <c r="P7">
-        <v>1.033570150017332</v>
+        <v>1.033570150017333</v>
       </c>
       <c r="Q7">
-        <v>22.81481635940516</v>
+        <v>22.81481635940514</v>
       </c>
       <c r="R7">
-        <v>-89.98391498208245</v>
+        <v>-89.98391498208235</v>
       </c>
       <c r="S7">
         <v>157.1900195359762</v>
@@ -1145,55 +1145,55 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>29.50985467837084</v>
+        <v>29.50985467837083</v>
       </c>
       <c r="D8">
-        <v>29.50985467837084</v>
+        <v>29.50985467837083</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>6.815009118473204</v>
+        <v>6.815009118473202</v>
       </c>
       <c r="G8">
-        <v>6.815009118473204</v>
+        <v>6.815009118473202</v>
       </c>
       <c r="H8">
-        <v>0.002680261932313766</v>
+        <v>0.00216826389269289</v>
       </c>
       <c r="I8">
-        <v>0.007676495104230187</v>
+        <v>0.007423284705210115</v>
       </c>
       <c r="J8">
         <v>0.001405778171205794</v>
       </c>
       <c r="K8">
-        <v>0.007321397045619365</v>
+        <v>0.007321397045619378</v>
       </c>
       <c r="L8">
-        <v>0.001405778171188655</v>
+        <v>0.001405778171188657</v>
       </c>
       <c r="M8">
-        <v>0.007321397045589348</v>
+        <v>0.007321397045589349</v>
       </c>
       <c r="N8">
-        <v>0.9526279648090317</v>
+        <v>0.9526279648090328</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>0.9526279648092565</v>
+        <v>0.9526279648092575</v>
       </c>
       <c r="Q8">
-        <v>-1.292152535891115E-11</v>
+        <v>-1.292993520603631E-11</v>
       </c>
       <c r="R8">
         <v>0</v>
       </c>
       <c r="S8">
-        <v>-179.999999999981</v>
+        <v>-179.9999999999811</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -1240,16 +1240,16 @@
         <v>1.03336277094941</v>
       </c>
       <c r="O9">
-        <v>0.8013810488327402</v>
+        <v>0.8013810488327404</v>
       </c>
       <c r="P9">
-        <v>1.033570150017332</v>
+        <v>1.033570150017333</v>
       </c>
       <c r="Q9">
-        <v>22.81481635940516</v>
+        <v>22.81481635940513</v>
       </c>
       <c r="R9">
-        <v>-89.98391498208245</v>
+        <v>-89.98391498208237</v>
       </c>
       <c r="S9">
         <v>157.1900195359762</v>
@@ -1701,19 +1701,19 @@
         <v>0.01369392767242736</v>
       </c>
       <c r="H8">
-        <v>0.002657050495199304</v>
+        <v>0.002145052455584837</v>
       </c>
       <c r="I8">
-        <v>0.007445544226858886</v>
+        <v>0.007192333827821748</v>
       </c>
       <c r="J8">
-        <v>0.001382566736038376</v>
+        <v>0.001382566736038385</v>
       </c>
       <c r="K8">
-        <v>0.007090446173215316</v>
+        <v>0.007090446173215331</v>
       </c>
       <c r="L8">
-        <v>0.001382566736026977</v>
+        <v>0.001382566736026993</v>
       </c>
       <c r="M8">
         <v>0.007090446173195246</v>
@@ -1971,7 +1971,7 @@
         <v>1.099479087110103</v>
       </c>
       <c r="P3">
-        <v>1.099717502166136</v>
+        <v>1.099717502166137</v>
       </c>
       <c r="Q3">
         <v>29.98367016303104</v>
@@ -2242,22 +2242,22 @@
         <v>0.01434529176646757</v>
       </c>
       <c r="H8">
-        <v>0.002680261932313766</v>
+        <v>0.00216826389269289</v>
       </c>
       <c r="I8">
-        <v>0.007676495104230187</v>
+        <v>0.007423284705210115</v>
       </c>
       <c r="J8">
         <v>0.001405778171205794</v>
       </c>
       <c r="K8">
-        <v>0.007321397045619365</v>
+        <v>0.007321397045619378</v>
       </c>
       <c r="L8">
-        <v>0.001405778171188655</v>
+        <v>0.001405778171188657</v>
       </c>
       <c r="M8">
-        <v>0.007321397045589348</v>
+        <v>0.007321397045589349</v>
       </c>
       <c r="N8">
         <v>1.100082664252146</v>
@@ -2447,22 +2447,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9151907893119887</v>
+        <v>0.9151907893119883</v>
       </c>
       <c r="O2">
-        <v>0.7128571052612477</v>
+        <v>0.712857105261248</v>
       </c>
       <c r="P2">
-        <v>0.8776436699748292</v>
+        <v>0.8776436699748285</v>
       </c>
       <c r="Q2">
-        <v>22.88086751500509</v>
+        <v>22.88086751500512</v>
       </c>
       <c r="R2">
-        <v>-93.28996606058699</v>
+        <v>-93.28996606058702</v>
       </c>
       <c r="S2">
-        <v>156.0806354489423</v>
+        <v>156.0806354489422</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -2506,19 +2506,19 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8894753503559816</v>
+        <v>0.8894753503559812</v>
       </c>
       <c r="O3">
         <v>0.6713200058608624</v>
       </c>
       <c r="P3">
-        <v>0.8876479269796576</v>
+        <v>0.8876479269796569</v>
       </c>
       <c r="Q3">
-        <v>22.1706772273978</v>
+        <v>22.17067722739783</v>
       </c>
       <c r="R3">
-        <v>-90.16844812169137</v>
+        <v>-90.16844812169141</v>
       </c>
       <c r="S3">
         <v>157.7812478886505</v>
@@ -2565,19 +2565,19 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8894753503584598</v>
+        <v>0.8894753503584596</v>
       </c>
       <c r="O4">
-        <v>0.6713200058984331</v>
+        <v>0.6713200058984332</v>
       </c>
       <c r="P4">
-        <v>0.8876479269913815</v>
+        <v>0.8876479269913806</v>
       </c>
       <c r="Q4">
-        <v>22.17067722864045</v>
+        <v>22.17067722864048</v>
       </c>
       <c r="R4">
-        <v>-90.16844812083106</v>
+        <v>-90.1684481208311</v>
       </c>
       <c r="S4">
         <v>157.7812478876488</v>
@@ -2624,19 +2624,19 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8287078948099389</v>
+        <v>0.8287078948099387</v>
       </c>
       <c r="O5">
-        <v>0.6190173487742737</v>
+        <v>0.6190173487742739</v>
       </c>
       <c r="P5">
-        <v>0.9265983111084939</v>
+        <v>0.9265983111084931</v>
       </c>
       <c r="Q5">
-        <v>21.60037830528558</v>
+        <v>21.60037830528561</v>
       </c>
       <c r="R5">
-        <v>-80.2879618148944</v>
+        <v>-80.28796181489444</v>
       </c>
       <c r="S5">
         <v>160.7773742491241</v>
@@ -2683,19 +2683,19 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8894753503584598</v>
+        <v>0.8894753503584596</v>
       </c>
       <c r="O6">
         <v>0.6713200058984331</v>
       </c>
       <c r="P6">
-        <v>0.8876479269913815</v>
+        <v>0.8876479269913806</v>
       </c>
       <c r="Q6">
-        <v>22.17067722864045</v>
+        <v>22.17067722864047</v>
       </c>
       <c r="R6">
-        <v>-90.16844812083106</v>
+        <v>-90.1684481208311</v>
       </c>
       <c r="S6">
         <v>157.7812478876488</v>
@@ -2742,19 +2742,19 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.8894753503149542</v>
+        <v>0.8894753503149539</v>
       </c>
       <c r="O7">
         <v>0.6713200059072644</v>
       </c>
       <c r="P7">
-        <v>0.8876479270383163</v>
+        <v>0.8876479270383154</v>
       </c>
       <c r="Q7">
-        <v>22.17067723009956</v>
+        <v>22.17067723009959</v>
       </c>
       <c r="R7">
-        <v>-90.16844811249253</v>
+        <v>-90.16844811249254</v>
       </c>
       <c r="S7">
         <v>157.7812478885684</v>
@@ -2777,40 +2777,40 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>5.584216265436999</v>
+        <v>5.584216265437</v>
       </c>
       <c r="G8">
-        <v>5.584216265436999</v>
+        <v>5.584216265437</v>
       </c>
       <c r="H8">
-        <v>0.004540640357537321</v>
+        <v>0.003557604122208292</v>
       </c>
       <c r="I8">
-        <v>0.007926334487991512</v>
+        <v>0.007673124089799144</v>
       </c>
       <c r="J8">
-        <v>0.002093407521764378</v>
+        <v>0.002093407521764388</v>
       </c>
       <c r="K8">
-        <v>0.007573622492677809</v>
+        <v>0.00757362249267782</v>
       </c>
       <c r="L8">
-        <v>0.002093407521783539</v>
+        <v>0.002093407521783568</v>
       </c>
       <c r="M8">
-        <v>0.007573622492710656</v>
+        <v>0.007573622492710651</v>
       </c>
       <c r="N8">
-        <v>0.822724123272736</v>
+        <v>0.8227241232727355</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>0.8227241232723459</v>
+        <v>0.8227241232723451</v>
       </c>
       <c r="Q8">
-        <v>-2.59904366751742E-12</v>
+        <v>-2.57968156054432E-12</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2860,19 +2860,19 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.8894753503149542</v>
+        <v>0.8894753503149539</v>
       </c>
       <c r="O9">
         <v>0.6713200059072644</v>
       </c>
       <c r="P9">
-        <v>0.8876479270383163</v>
+        <v>0.8876479270383154</v>
       </c>
       <c r="Q9">
-        <v>22.17067723009956</v>
+        <v>22.17067723009958</v>
       </c>
       <c r="R9">
-        <v>-90.16844811249253</v>
+        <v>-90.16844811249254</v>
       </c>
       <c r="S9">
         <v>157.7812478885684</v>
@@ -2988,22 +2988,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8670228409438512</v>
+        <v>0.867022840943851</v>
       </c>
       <c r="O2">
         <v>0.6753383008315212</v>
       </c>
       <c r="P2">
-        <v>0.8314518862782836</v>
+        <v>0.8314518862782829</v>
       </c>
       <c r="Q2">
-        <v>22.8808675150051</v>
+        <v>22.88086751500511</v>
       </c>
       <c r="R2">
-        <v>-93.28996606058699</v>
+        <v>-93.28996606058702</v>
       </c>
       <c r="S2">
-        <v>156.0806354489423</v>
+        <v>156.0806354489422</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -3047,19 +3047,19 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8426608464830934</v>
+        <v>0.8426608464830928</v>
       </c>
       <c r="O3">
-        <v>0.6359873651061265</v>
+        <v>0.6359873651061263</v>
       </c>
       <c r="P3">
-        <v>0.8409296033086084</v>
+        <v>0.8409296033086079</v>
       </c>
       <c r="Q3">
-        <v>22.1706772273978</v>
+        <v>22.17067722739782</v>
       </c>
       <c r="R3">
-        <v>-90.16844812169137</v>
+        <v>-90.16844812169141</v>
       </c>
       <c r="S3">
         <v>157.7812478886505</v>
@@ -3106,19 +3106,19 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.842660846485441</v>
+        <v>0.8426608464854409</v>
       </c>
       <c r="O4">
         <v>0.6359873651417198</v>
       </c>
       <c r="P4">
-        <v>0.8409296033197154</v>
+        <v>0.8409296033197147</v>
       </c>
       <c r="Q4">
-        <v>22.17067722864045</v>
+        <v>22.17067722864049</v>
       </c>
       <c r="R4">
-        <v>-90.16844812083106</v>
+        <v>-90.1684481208311</v>
       </c>
       <c r="S4">
         <v>157.7812478876488</v>
@@ -3165,19 +3165,19 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.7850916788737171</v>
+        <v>0.7850916788737168</v>
       </c>
       <c r="O5">
-        <v>0.5864374801360024</v>
+        <v>0.5864374801360025</v>
       </c>
       <c r="P5">
-        <v>0.8778299667056503</v>
+        <v>0.8778299667056495</v>
       </c>
       <c r="Q5">
-        <v>21.60037830528558</v>
+        <v>21.60037830528562</v>
       </c>
       <c r="R5">
-        <v>-80.2879618148944</v>
+        <v>-80.28796181489444</v>
       </c>
       <c r="S5">
         <v>160.7773742491241</v>
@@ -3224,19 +3224,19 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.842660846485441</v>
+        <v>0.8426608464854409</v>
       </c>
       <c r="O6">
-        <v>0.6359873651417197</v>
+        <v>0.6359873651417198</v>
       </c>
       <c r="P6">
-        <v>0.8409296033197152</v>
+        <v>0.8409296033197147</v>
       </c>
       <c r="Q6">
-        <v>22.17067722864045</v>
+        <v>22.17067722864048</v>
       </c>
       <c r="R6">
-        <v>-90.16844812083106</v>
+        <v>-90.1684481208311</v>
       </c>
       <c r="S6">
         <v>157.7812478876488</v>
@@ -3283,19 +3283,19 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.842660846444225</v>
+        <v>0.8426608464442248</v>
       </c>
       <c r="O7">
         <v>0.6359873651500861</v>
       </c>
       <c r="P7">
-        <v>0.8409296033641798</v>
+        <v>0.840929603364179</v>
       </c>
       <c r="Q7">
-        <v>22.17067723009956</v>
+        <v>22.17067723009959</v>
       </c>
       <c r="R7">
-        <v>-90.16844811249253</v>
+        <v>-90.16844811249254</v>
       </c>
       <c r="S7">
         <v>157.7812478885684</v>
@@ -3324,34 +3324,34 @@
         <v>5.290310072442756</v>
       </c>
       <c r="H8">
-        <v>0.004540640357537321</v>
+        <v>0.003557604122208292</v>
       </c>
       <c r="I8">
-        <v>0.007926334487991512</v>
+        <v>0.007673124089799144</v>
       </c>
       <c r="J8">
-        <v>0.002093407521764378</v>
+        <v>0.002093407521764388</v>
       </c>
       <c r="K8">
-        <v>0.007573622492677809</v>
+        <v>0.00757362249267782</v>
       </c>
       <c r="L8">
-        <v>0.002093407521783539</v>
+        <v>0.002093407521783568</v>
       </c>
       <c r="M8">
-        <v>0.007573622492710656</v>
+        <v>0.007573622492710651</v>
       </c>
       <c r="N8">
-        <v>0.779422842759616</v>
+        <v>0.7794228427596154</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>0.7794228427592463</v>
+        <v>0.7794228427592457</v>
       </c>
       <c r="Q8">
-        <v>-2.595660463494697E-12</v>
+        <v>-2.576112887069369E-12</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -3401,19 +3401,19 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.842660846444225</v>
+        <v>0.8426608464442249</v>
       </c>
       <c r="O9">
         <v>0.6359873651500861</v>
       </c>
       <c r="P9">
-        <v>0.8409296033641798</v>
+        <v>0.840929603364179</v>
       </c>
       <c r="Q9">
-        <v>22.17067723009956</v>
+        <v>22.17067723009959</v>
       </c>
       <c r="R9">
-        <v>-90.16844811249253</v>
+        <v>-90.16844811249254</v>
       </c>
       <c r="S9">
         <v>157.7812478885684</v>
@@ -3865,22 +3865,22 @@
         <v>0.01238679212016367</v>
       </c>
       <c r="H8">
-        <v>0.004540640357537321</v>
+        <v>0.003557604122208292</v>
       </c>
       <c r="I8">
-        <v>0.007926334487991512</v>
+        <v>0.007673124089799144</v>
       </c>
       <c r="J8">
-        <v>0.002093407521764378</v>
+        <v>0.002093407521764388</v>
       </c>
       <c r="K8">
-        <v>0.007573622492677809</v>
+        <v>0.00757362249267782</v>
       </c>
       <c r="L8">
-        <v>0.002093407521783539</v>
+        <v>0.002093407521783568</v>
       </c>
       <c r="M8">
-        <v>0.007573622492710656</v>
+        <v>0.007573622492710651</v>
       </c>
       <c r="N8">
         <v>0.9499911223989927</v>
@@ -4406,22 +4406,22 @@
         <v>0.01173485552917215</v>
       </c>
       <c r="H8">
-        <v>0.004540640357537321</v>
+        <v>0.003557604122208292</v>
       </c>
       <c r="I8">
-        <v>0.007926334487991512</v>
+        <v>0.007673124089799144</v>
       </c>
       <c r="J8">
-        <v>0.002093407521764378</v>
+        <v>0.002093407521764388</v>
       </c>
       <c r="K8">
-        <v>0.007573622492677809</v>
+        <v>0.00757362249267782</v>
       </c>
       <c r="L8">
-        <v>0.002093407521783539</v>
+        <v>0.002093407521783568</v>
       </c>
       <c r="M8">
-        <v>0.007573622492710656</v>
+        <v>0.007573622492710651</v>
       </c>
       <c r="N8">
         <v>0.8999915770929219</v>
@@ -4614,22 +4614,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.918079323424824</v>
+        <v>0.9171621052337379</v>
       </c>
       <c r="O2">
-        <v>1.04999995231535</v>
+        <v>1.049999952315338</v>
       </c>
       <c r="P2">
-        <v>0.9416612294398952</v>
+        <v>0.9379496137042669</v>
       </c>
       <c r="Q2">
-        <v>33.30519410596439</v>
+        <v>33.53153627131392</v>
       </c>
       <c r="R2">
-        <v>-89.9999999999964</v>
+        <v>-89.99999999999639</v>
       </c>
       <c r="S2">
-        <v>144.5703399400573</v>
+        <v>144.5979893024127</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -4676,22 +4676,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9057672196134799</v>
+        <v>0.9052014084333547</v>
       </c>
       <c r="O3">
-        <v>1.04999995231535</v>
+        <v>1.049999952315338</v>
       </c>
       <c r="P3">
-        <v>0.91626521283733</v>
+        <v>0.9120586767023519</v>
       </c>
       <c r="Q3">
-        <v>34.71976263906428</v>
+        <v>34.98947327542609</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999638</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S3">
-        <v>144.3438877646951</v>
+        <v>144.3997149407726</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -4738,22 +4738,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9057672196263914</v>
+        <v>0.9052014084464479</v>
       </c>
       <c r="O4">
-        <v>1.04999995231535</v>
+        <v>1.049999952315338</v>
       </c>
       <c r="P4">
-        <v>0.9162652128427821</v>
+        <v>0.9120586767081426</v>
       </c>
       <c r="Q4">
-        <v>34.71976263898934</v>
+        <v>34.98947327532949</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999638</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S4">
-        <v>144.3438877654307</v>
+        <v>144.3997149415165</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -4800,22 +4800,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9023556971450637</v>
+        <v>0.9029160766055095</v>
       </c>
       <c r="O5">
-        <v>1.04999995231535</v>
+        <v>1.049999952315338</v>
       </c>
       <c r="P5">
-        <v>0.8711208258709717</v>
+        <v>0.8664236793427247</v>
       </c>
       <c r="Q5">
-        <v>37.6649640120446</v>
+        <v>37.98838390345735</v>
       </c>
       <c r="R5">
         <v>-89.99999999999638</v>
       </c>
       <c r="S5">
-        <v>145.0828727973339</v>
+        <v>145.2182126944608</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -4862,22 +4862,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9057672196263913</v>
+        <v>0.9052014084464479</v>
       </c>
       <c r="O6">
-        <v>1.04999995231535</v>
+        <v>1.049999952315338</v>
       </c>
       <c r="P6">
-        <v>0.9162652128427818</v>
+        <v>0.9120586767081426</v>
       </c>
       <c r="Q6">
-        <v>34.71976263898935</v>
+        <v>34.98947327532949</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999638</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S6">
-        <v>144.3438877654307</v>
+        <v>144.3997149415165</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -4924,22 +4924,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.9057672196599131</v>
+        <v>0.9052014084816167</v>
       </c>
       <c r="O7">
-        <v>1.04999995231535</v>
+        <v>1.049999952315338</v>
       </c>
       <c r="P7">
-        <v>0.9162652128125868</v>
+        <v>0.9120586766784313</v>
       </c>
       <c r="Q7">
-        <v>34.71976264177326</v>
+        <v>34.98947327810781</v>
       </c>
       <c r="R7">
-        <v>-89.99999999999638</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S7">
-        <v>144.3438877683294</v>
+        <v>144.3997149445166</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -4950,7 +4950,7 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>32.6277242531857</v>
+        <v>33.17197678509493</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -4959,7 +4959,7 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>7.535050264529654</v>
+        <v>7.660740004724551</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -4968,43 +4968,43 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0.002657050495199364</v>
+        <v>0.002145052455584889</v>
       </c>
       <c r="I8">
-        <v>0.007445544226858362</v>
+        <v>0.007192333827821216</v>
       </c>
       <c r="J8">
-        <v>0.001382566736058361</v>
+        <v>0.001382566736058353</v>
       </c>
       <c r="K8">
-        <v>0.007090446173195478</v>
+        <v>0.007090446173195473</v>
       </c>
       <c r="L8">
-        <v>0.001382566736027095</v>
+        <v>0.00138256673602709</v>
       </c>
       <c r="M8">
-        <v>0.007090446173195125</v>
+        <v>0.007090446173195104</v>
       </c>
       <c r="N8">
-        <v>0.5888568561193094</v>
+        <v>0.5929331444146656</v>
       </c>
       <c r="O8">
-        <v>1.049999952313886</v>
+        <v>1.049999952313865</v>
       </c>
       <c r="P8">
-        <v>0.6421899305339801</v>
+        <v>0.6272038381499898</v>
       </c>
       <c r="Q8">
-        <v>56.9783060568449</v>
+        <v>58.41309028743814</v>
       </c>
       <c r="R8">
-        <v>-89.99999999999648</v>
+        <v>-89.99999999999646</v>
       </c>
       <c r="S8">
-        <v>119.9800602072594</v>
+        <v>119.6810343087593</v>
       </c>
       <c r="T8">
-        <v>32.62772425318569</v>
+        <v>33.17197678509493</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -5048,22 +5048,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.9057672196599131</v>
+        <v>0.9052014084816167</v>
       </c>
       <c r="O9">
-        <v>1.04999995231535</v>
+        <v>1.049999952315338</v>
       </c>
       <c r="P9">
-        <v>0.9162652128125868</v>
+        <v>0.912058676678431</v>
       </c>
       <c r="Q9">
-        <v>34.71976264177326</v>
+        <v>34.98947327810781</v>
       </c>
       <c r="R9">
-        <v>-89.99999999999638</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S9">
-        <v>144.3438877683294</v>
+        <v>144.3997149445166</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -5182,22 +5182,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9661589806972211</v>
+        <v>0.9652795302754225</v>
       </c>
       <c r="O2">
-        <v>1.100000023840909</v>
+        <v>1.100000023840898</v>
       </c>
       <c r="P2">
-        <v>0.9893216119570089</v>
+        <v>0.9856706301434143</v>
       </c>
       <c r="Q2">
-        <v>33.22684099248068</v>
+        <v>33.43907657332316</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999639</v>
+        <v>-89.9999999999964</v>
       </c>
       <c r="S2">
-        <v>144.7779354185199</v>
+        <v>144.8063775969255</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -5244,22 +5244,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9537072651466403</v>
+        <v>0.95317468305126</v>
       </c>
       <c r="O3">
-        <v>1.100000023840909</v>
+        <v>1.100000023840898</v>
       </c>
       <c r="P3">
-        <v>0.9634843433900694</v>
+        <v>0.9593512472120813</v>
       </c>
       <c r="Q3">
-        <v>34.59438506088102</v>
+        <v>34.84692290335759</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999636</v>
+        <v>-89.99999999999638</v>
       </c>
       <c r="S3">
-        <v>144.5714030436847</v>
+        <v>144.6267116676425</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5306,22 +5306,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9537072651597581</v>
+        <v>0.9531746830645554</v>
       </c>
       <c r="O4">
-        <v>1.100000023840909</v>
+        <v>1.100000023840898</v>
       </c>
       <c r="P4">
-        <v>0.9634843433957095</v>
+        <v>0.9593512472180563</v>
       </c>
       <c r="Q4">
-        <v>34.59438506080698</v>
+        <v>34.84692290326333</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999636</v>
+        <v>-89.99999999999638</v>
       </c>
       <c r="S4">
-        <v>144.5714030443928</v>
+        <v>144.626711668358</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5368,22 +5368,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9503022843721648</v>
+        <v>0.9508748496589552</v>
       </c>
       <c r="O5">
-        <v>1.100000023840909</v>
+        <v>1.100000023840898</v>
       </c>
       <c r="P5">
-        <v>0.9177076796232401</v>
+        <v>0.9131051000940402</v>
       </c>
       <c r="Q5">
-        <v>37.43684045220055</v>
+        <v>37.73925042195317</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999636</v>
+        <v>-89.99999999999639</v>
       </c>
       <c r="S5">
-        <v>145.3082093239078</v>
+        <v>145.4382545631504</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5430,22 +5430,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.953707265159758</v>
+        <v>0.9531746830645554</v>
       </c>
       <c r="O6">
-        <v>1.100000023840909</v>
+        <v>1.100000023840898</v>
       </c>
       <c r="P6">
-        <v>0.9634843433957095</v>
+        <v>0.9593512472180562</v>
       </c>
       <c r="Q6">
-        <v>34.59438506080697</v>
+        <v>34.84692290326332</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999636</v>
+        <v>-89.99999999999638</v>
       </c>
       <c r="S6">
-        <v>144.5714030443928</v>
+        <v>144.626711668358</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -5492,22 +5492,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.9537072651955484</v>
+        <v>0.9531746831020385</v>
       </c>
       <c r="O7">
-        <v>1.100000023840909</v>
+        <v>1.100000023840898</v>
       </c>
       <c r="P7">
-        <v>0.9634843433639775</v>
+        <v>0.9593512471868422</v>
       </c>
       <c r="Q7">
-        <v>34.59438506361701</v>
+        <v>34.84692290606753</v>
       </c>
       <c r="R7">
-        <v>-89.99999999999636</v>
+        <v>-89.99999999999638</v>
       </c>
       <c r="S7">
-        <v>144.5714030473434</v>
+        <v>144.6267116714074</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -5518,7 +5518,7 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>33.15649393464221</v>
+        <v>33.690013083823</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -5527,7 +5527,7 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>7.657164393520588</v>
+        <v>7.780375365115516</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -5536,43 +5536,43 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0.002680261932313829</v>
+        <v>0.002168263892692974</v>
       </c>
       <c r="I8">
-        <v>0.007676495104229606</v>
+        <v>0.007423284705209505</v>
       </c>
       <c r="J8">
-        <v>0.001405778171204621</v>
+        <v>0.00140577817120463</v>
       </c>
       <c r="K8">
-        <v>0.00732139704558959</v>
+        <v>0.007321397045589575</v>
       </c>
       <c r="L8">
-        <v>0.001405778171188779</v>
+        <v>0.001405778171188792</v>
       </c>
       <c r="M8">
-        <v>0.007321397045589218</v>
+        <v>0.007321397045589203</v>
       </c>
       <c r="N8">
-        <v>0.6172750535653924</v>
+        <v>0.6215203991532136</v>
       </c>
       <c r="O8">
-        <v>1.10000002384084</v>
+        <v>1.100000023840834</v>
       </c>
       <c r="P8">
-        <v>0.6716391779829419</v>
+        <v>0.6563854449693051</v>
       </c>
       <c r="Q8">
-        <v>57.078355237089</v>
+        <v>58.46734441056156</v>
       </c>
       <c r="R8">
-        <v>-89.99999999999646</v>
+        <v>-89.99999999999649</v>
       </c>
       <c r="S8">
-        <v>119.9669292089925</v>
+        <v>119.6832836072256</v>
       </c>
       <c r="T8">
-        <v>33.15649393464221</v>
+        <v>33.690013083823</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -5616,22 +5616,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.9537072651955484</v>
+        <v>0.9531746831020383</v>
       </c>
       <c r="O9">
-        <v>1.100000023840909</v>
+        <v>1.100000023840898</v>
       </c>
       <c r="P9">
-        <v>0.9634843433639775</v>
+        <v>0.9593512471868422</v>
       </c>
       <c r="Q9">
-        <v>34.59438506361701</v>
+        <v>34.84692290606753</v>
       </c>
       <c r="R9">
-        <v>-89.99999999999636</v>
+        <v>-89.99999999999638</v>
       </c>
       <c r="S9">
-        <v>144.5714030473434</v>
+        <v>144.6267116714074</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -5750,22 +5750,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.049851163902369</v>
+        <v>1.049851159901853</v>
       </c>
       <c r="O2">
         <v>1.049999952316283</v>
       </c>
       <c r="P2">
-        <v>1.049946572362265</v>
+        <v>1.049946569785278</v>
       </c>
       <c r="Q2">
-        <v>29.99867631252171</v>
+        <v>29.99867634888799</v>
       </c>
       <c r="R2">
         <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>149.9923065866064</v>
+        <v>149.9923064157113</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -5812,22 +5812,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.049827033222095</v>
+        <v>1.049827028710248</v>
       </c>
       <c r="O3">
         <v>1.049999952316283</v>
       </c>
       <c r="P3">
-        <v>1.049924125365282</v>
+        <v>1.049924122087718</v>
       </c>
       <c r="Q3">
-        <v>29.9993306672146</v>
+        <v>29.99933073162638</v>
       </c>
       <c r="R3">
         <v>-89.99999999999635</v>
       </c>
       <c r="S3">
-        <v>149.9914931740389</v>
+        <v>149.9914929929866</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5874,22 +5874,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.049827033222106</v>
+        <v>1.049827028710259</v>
       </c>
       <c r="O4">
         <v>1.049999952316283</v>
       </c>
       <c r="P4">
-        <v>1.049924125365282</v>
+        <v>1.049924122087718</v>
       </c>
       <c r="Q4">
-        <v>29.99933066721498</v>
+        <v>29.99933073162677</v>
       </c>
       <c r="R4">
         <v>-89.99999999999635</v>
       </c>
       <c r="S4">
-        <v>149.9914931740396</v>
+        <v>149.9914929929873</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5936,22 +5936,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.04979475283137</v>
+        <v>1.049794747814466</v>
       </c>
       <c r="O5">
         <v>1.049999952316283</v>
       </c>
       <c r="P5">
-        <v>1.049876147185021</v>
+        <v>1.049876142602301</v>
       </c>
       <c r="Q5">
-        <v>30.00133720457854</v>
+        <v>30.0013373353376</v>
       </c>
       <c r="R5">
         <v>-89.99999999999635</v>
       </c>
       <c r="S5">
-        <v>149.9909703296296</v>
+        <v>149.9909701578482</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5998,22 +5998,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>1.049827033222106</v>
+        <v>1.049827028710259</v>
       </c>
       <c r="O6">
         <v>1.049999952316283</v>
       </c>
       <c r="P6">
-        <v>1.049924125365282</v>
+        <v>1.049924122087718</v>
       </c>
       <c r="Q6">
-        <v>29.99933066721498</v>
+        <v>29.99933073162677</v>
       </c>
       <c r="R6">
         <v>-89.99999999999635</v>
       </c>
       <c r="S6">
-        <v>149.9914931740396</v>
+        <v>149.9914929929873</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -6060,22 +6060,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>1.049827033222108</v>
+        <v>1.049827028710261</v>
       </c>
       <c r="O7">
         <v>1.049999952316283</v>
       </c>
       <c r="P7">
-        <v>1.049924125365232</v>
+        <v>1.049924122087668</v>
       </c>
       <c r="Q7">
-        <v>29.99933066721815</v>
+        <v>29.99933073162993</v>
       </c>
       <c r="R7">
         <v>-89.99999999999635</v>
       </c>
       <c r="S7">
-        <v>149.9914931740413</v>
+        <v>149.991492992989</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -6086,7 +6086,7 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>0.03426195906811658</v>
+        <v>0.03426283206025032</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -6095,7 +6095,7 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0.00791246063428127</v>
+        <v>0.007912662243181639</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -6104,43 +6104,43 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0.002657050495199364</v>
+        <v>0.002145052455584889</v>
       </c>
       <c r="I8">
-        <v>0.007445544226858362</v>
+        <v>0.007192333827821216</v>
       </c>
       <c r="J8">
-        <v>0.001382566736058361</v>
+        <v>0.001382566736058353</v>
       </c>
       <c r="K8">
-        <v>0.007090446173195478</v>
+        <v>0.007090446173195473</v>
       </c>
       <c r="L8">
-        <v>0.001382566736027095</v>
+        <v>0.00138256673602709</v>
       </c>
       <c r="M8">
-        <v>0.007090446173195125</v>
+        <v>0.007090446173195104</v>
       </c>
       <c r="N8">
-        <v>1.049382642766533</v>
+        <v>1.049382626670754</v>
       </c>
       <c r="O8">
         <v>1.049999952316282</v>
       </c>
       <c r="P8">
-        <v>1.049728222110565</v>
+        <v>1.049728210391031</v>
       </c>
       <c r="Q8">
-        <v>29.99768130131084</v>
+        <v>29.99768153315805</v>
       </c>
       <c r="R8">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S8">
-        <v>149.9696613867876</v>
+        <v>149.9696607415288</v>
       </c>
       <c r="T8">
-        <v>0.03426195906811659</v>
+        <v>0.03426283206025032</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -6184,22 +6184,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>1.049827033222108</v>
+        <v>1.049827028710261</v>
       </c>
       <c r="O9">
         <v>1.049999952316283</v>
       </c>
       <c r="P9">
-        <v>1.049924125365232</v>
+        <v>1.049924122087668</v>
       </c>
       <c r="Q9">
-        <v>29.99933066721815</v>
+        <v>29.99933073162993</v>
       </c>
       <c r="R9">
         <v>-89.99999999999635</v>
       </c>
       <c r="S9">
-        <v>149.9914931740413</v>
+        <v>149.991492992989</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -6535,22 +6535,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.099844153687694</v>
+        <v>1.099844149496921</v>
       </c>
       <c r="O2">
         <v>1.100000023841857</v>
       </c>
       <c r="P2">
-        <v>1.099944100338489</v>
+        <v>1.099944097638789</v>
       </c>
       <c r="Q2">
-        <v>29.99867651456935</v>
+        <v>29.99867655094284</v>
       </c>
       <c r="R2">
         <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>149.9923068424676</v>
+        <v>149.992306671587</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -6597,22 +6597,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.099818874828489</v>
+        <v>1.099818870102083</v>
       </c>
       <c r="O3">
         <v>1.100000023841857</v>
       </c>
       <c r="P3">
-        <v>1.099920584708768</v>
+        <v>1.09992058127516</v>
       </c>
       <c r="Q3">
-        <v>29.99933087995546</v>
+        <v>29.99933094437418</v>
       </c>
       <c r="R3">
         <v>-89.99999999999635</v>
       </c>
       <c r="S3">
-        <v>149.9914934759751</v>
+        <v>149.9914932949395</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -6659,22 +6659,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.099818874828501</v>
+        <v>1.099818870102096</v>
       </c>
       <c r="O4">
         <v>1.100000023841857</v>
       </c>
       <c r="P4">
-        <v>1.099920584708768</v>
+        <v>1.09992058127516</v>
       </c>
       <c r="Q4">
-        <v>29.99933087995583</v>
+        <v>29.99933094437456</v>
       </c>
       <c r="R4">
         <v>-89.99999999999635</v>
       </c>
       <c r="S4">
-        <v>149.9914934759759</v>
+        <v>149.9914932949403</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -6721,22 +6721,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.09978505893212</v>
+        <v>1.099785053676686</v>
       </c>
       <c r="O5">
         <v>1.100000023841857</v>
       </c>
       <c r="P5">
-        <v>1.099870322918549</v>
+        <v>1.09987031811771</v>
       </c>
       <c r="Q5">
-        <v>30.00133740288164</v>
+        <v>30.00133753364541</v>
       </c>
       <c r="R5">
         <v>-89.99999999999635</v>
       </c>
       <c r="S5">
-        <v>149.990970699168</v>
+        <v>149.9909705274057</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -6783,22 +6783,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>1.099818874828501</v>
+        <v>1.099818870102096</v>
       </c>
       <c r="O6">
         <v>1.100000023841857</v>
       </c>
       <c r="P6">
-        <v>1.099920584708768</v>
+        <v>1.09992058127516</v>
       </c>
       <c r="Q6">
-        <v>29.99933087995583</v>
+        <v>29.99933094437456</v>
       </c>
       <c r="R6">
         <v>-89.99999999999635</v>
       </c>
       <c r="S6">
-        <v>149.9914934759759</v>
+        <v>149.9914932949403</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -6845,22 +6845,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>1.099818874828503</v>
+        <v>1.099818870102097</v>
       </c>
       <c r="O7">
         <v>1.100000023841857</v>
       </c>
       <c r="P7">
-        <v>1.099920584708714</v>
+        <v>1.099920581275105</v>
       </c>
       <c r="Q7">
-        <v>29.99933087995915</v>
+        <v>29.99933094437788</v>
       </c>
       <c r="R7">
         <v>-89.99999999999635</v>
       </c>
       <c r="S7">
-        <v>149.9914934759776</v>
+        <v>149.991493294942</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -6871,7 +6871,7 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>0.03589257149490889</v>
+        <v>0.03589348600526392</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -6880,7 +6880,7 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0.008289034449313651</v>
+        <v>0.00828924564643666</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -6889,43 +6889,43 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0.002680261932313829</v>
+        <v>0.002168263892692974</v>
       </c>
       <c r="I8">
-        <v>0.007676495104229606</v>
+        <v>0.007423284705209505</v>
       </c>
       <c r="J8">
-        <v>0.001405778171204621</v>
+        <v>0.00140577817120463</v>
       </c>
       <c r="K8">
-        <v>0.00732139704558959</v>
+        <v>0.007321397045589575</v>
       </c>
       <c r="L8">
-        <v>0.001405778171188779</v>
+        <v>0.001405778171188792</v>
       </c>
       <c r="M8">
-        <v>0.007321397045589218</v>
+        <v>0.007321397045589203</v>
       </c>
       <c r="N8">
-        <v>1.099332775846172</v>
+        <v>1.099332758432306</v>
       </c>
       <c r="O8">
         <v>1.100000023841857</v>
       </c>
       <c r="P8">
-        <v>1.099707973325898</v>
+        <v>1.099707960692537</v>
       </c>
       <c r="Q8">
-        <v>29.99750792371078</v>
+        <v>29.99750816039741</v>
       </c>
       <c r="R8">
-        <v>-89.99999999999635</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S8">
-        <v>149.9686476375806</v>
+        <v>149.968646969826</v>
       </c>
       <c r="T8">
-        <v>0.03589257149490889</v>
+        <v>0.03589348600526392</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -6969,22 +6969,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>1.099818874828503</v>
+        <v>1.099818870102097</v>
       </c>
       <c r="O9">
         <v>1.100000023841857</v>
       </c>
       <c r="P9">
-        <v>1.099920584708714</v>
+        <v>1.099920581275105</v>
       </c>
       <c r="Q9">
-        <v>29.99933087995915</v>
+        <v>29.99933094437788</v>
       </c>
       <c r="R9">
         <v>-89.99999999999635</v>
       </c>
       <c r="S9">
-        <v>149.9914934759776</v>
+        <v>149.991493294942</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -7103,22 +7103,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8218631616770085</v>
+        <v>0.8203517413149306</v>
       </c>
       <c r="O2">
-        <v>0.9499999880783462</v>
+        <v>0.9499999880783081</v>
       </c>
       <c r="P2">
-        <v>0.8608691550326996</v>
+        <v>0.8552759047137356</v>
       </c>
       <c r="Q2">
-        <v>32.40644770774409</v>
+        <v>32.78411255783824</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999643</v>
+        <v>-89.9999999999964</v>
       </c>
       <c r="S2">
-        <v>143.7082815813156</v>
+        <v>143.7444304857125</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -7165,22 +7165,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8123718539960552</v>
+        <v>0.8119016180263244</v>
       </c>
       <c r="O3">
-        <v>0.9499999880783461</v>
+        <v>0.949999988078308</v>
       </c>
       <c r="P3">
-        <v>0.8299562171384707</v>
+        <v>0.8237000906498112</v>
       </c>
       <c r="Q3">
-        <v>34.47158198636681</v>
+        <v>34.92729804453938</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999638</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S3">
-        <v>143.7980514663659</v>
+        <v>143.9141574508503</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -7227,22 +7227,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8123718540168461</v>
+        <v>0.8119016180473575</v>
       </c>
       <c r="O4">
-        <v>0.9499999880783461</v>
+        <v>0.9499999880783081</v>
       </c>
       <c r="P4">
-        <v>0.8299562171503722</v>
+        <v>0.8237000906626525</v>
       </c>
       <c r="Q4">
-        <v>34.47158198599157</v>
+        <v>34.92729804409172</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999638</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S4">
-        <v>143.7980514675988</v>
+        <v>143.9141574520902</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -7289,22 +7289,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8143738944206788</v>
+        <v>0.8169462903178869</v>
       </c>
       <c r="O5">
-        <v>0.949999988078346</v>
+        <v>0.9499999880783081</v>
       </c>
       <c r="P5">
-        <v>0.7661014189189572</v>
+        <v>0.7592688030973064</v>
       </c>
       <c r="Q5">
-        <v>39.24052857416536</v>
+        <v>39.7920801981398</v>
       </c>
       <c r="R5">
         <v>-89.99999999999638</v>
       </c>
       <c r="S5">
-        <v>145.4163851967612</v>
+        <v>145.7654013218176</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7351,22 +7351,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.812371854016846</v>
+        <v>0.8119016180473575</v>
       </c>
       <c r="O6">
-        <v>0.9499999880783461</v>
+        <v>0.9499999880783081</v>
       </c>
       <c r="P6">
-        <v>0.829956217150372</v>
+        <v>0.8237000906626525</v>
       </c>
       <c r="Q6">
-        <v>34.47158198599158</v>
+        <v>34.92729804409172</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999638</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S6">
-        <v>143.7980514675988</v>
+        <v>143.9141574520902</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -7413,22 +7413,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.8123718540475295</v>
+        <v>0.811901618080673</v>
       </c>
       <c r="O7">
-        <v>0.949999988078346</v>
+        <v>0.9499999880783081</v>
       </c>
       <c r="P7">
-        <v>0.8299562171184566</v>
+        <v>0.8237000906316351</v>
       </c>
       <c r="Q7">
-        <v>34.47158198913591</v>
+        <v>34.92729804721551</v>
       </c>
       <c r="R7">
-        <v>-89.99999999999638</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S7">
-        <v>143.7980514706162</v>
+        <v>143.9141574552833</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -7439,7 +7439,7 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>26.68044332957213</v>
+        <v>27.31186664489169</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -7448,7 +7448,7 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>6.161584547185575</v>
+        <v>6.307405517787416</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -7457,43 +7457,43 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0.004540640357537415</v>
+        <v>0.003557604122208396</v>
       </c>
       <c r="I8">
-        <v>0.007926334487990933</v>
+        <v>0.007673124089798526</v>
       </c>
       <c r="J8">
-        <v>0.002093407521777885</v>
+        <v>0.002093407521777895</v>
       </c>
       <c r="K8">
-        <v>0.007573622492710872</v>
+        <v>0.007573622492710861</v>
       </c>
       <c r="L8">
-        <v>0.002093407521783731</v>
+        <v>0.002093407521783739</v>
       </c>
       <c r="M8">
-        <v>0.007573622492710515</v>
+        <v>0.007573622492710481</v>
       </c>
       <c r="N8">
-        <v>0.5222305157832697</v>
+        <v>0.5288772534992601</v>
       </c>
       <c r="O8">
-        <v>0.9499999880783653</v>
+        <v>0.9499999880783313</v>
       </c>
       <c r="P8">
-        <v>0.6034471465751603</v>
+        <v>0.5816246050513872</v>
       </c>
       <c r="Q8">
-        <v>54.82746094553926</v>
+        <v>57.12287474676724</v>
       </c>
       <c r="R8">
         <v>-89.99999999999655</v>
       </c>
       <c r="S8">
-        <v>119.9016405334565</v>
+        <v>119.5780865591122</v>
       </c>
       <c r="T8">
-        <v>26.68044332957214</v>
+        <v>27.31186664489169</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -7537,22 +7537,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.8123718540475292</v>
+        <v>0.811901618080673</v>
       </c>
       <c r="O9">
-        <v>0.9499999880783461</v>
+        <v>0.949999988078308</v>
       </c>
       <c r="P9">
-        <v>0.8299562171184566</v>
+        <v>0.8237000906316351</v>
       </c>
       <c r="Q9">
-        <v>34.47158198913593</v>
+        <v>34.92729804721551</v>
       </c>
       <c r="R9">
-        <v>-89.99999999999638</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S9">
-        <v>143.7980514706162</v>
+        <v>143.9141574552833</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -7671,22 +7671,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.7786071949434566</v>
+        <v>0.7771753230414521</v>
       </c>
       <c r="O2">
-        <v>0.8999999761574552</v>
+        <v>0.8999999761574192</v>
       </c>
       <c r="P2">
-        <v>0.8155602407652055</v>
+        <v>0.8102613721158566</v>
       </c>
       <c r="Q2">
-        <v>32.40644770774409</v>
+        <v>32.78411255783824</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999643</v>
+        <v>-89.9999999999964</v>
       </c>
       <c r="S2">
-        <v>143.7082815813156</v>
+        <v>143.7444304857125</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -7733,22 +7733,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.7696154298973961</v>
+        <v>0.7691699431954414</v>
       </c>
       <c r="O3">
-        <v>0.8999999761574552</v>
+        <v>0.8999999761574192</v>
       </c>
       <c r="P3">
-        <v>0.7862743000105742</v>
+        <v>0.7803474434197433</v>
       </c>
       <c r="Q3">
-        <v>34.47158198636681</v>
+        <v>34.92729804453938</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999639</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S3">
-        <v>143.7980514663659</v>
+        <v>143.9141574508503</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -7795,22 +7795,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.7696154299170926</v>
+        <v>0.7691699432153672</v>
       </c>
       <c r="O4">
-        <v>0.8999999761574552</v>
+        <v>0.8999999761574192</v>
       </c>
       <c r="P4">
-        <v>0.7862743000218492</v>
+        <v>0.7803474434319086</v>
       </c>
       <c r="Q4">
-        <v>34.47158198599157</v>
+        <v>34.92729804409172</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999639</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S4">
-        <v>143.7980514675988</v>
+        <v>143.9141574520902</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -7857,22 +7857,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.7715120997469106</v>
+        <v>0.7739491063523928</v>
       </c>
       <c r="O5">
-        <v>0.8999999761574552</v>
+        <v>0.8999999761574192</v>
       </c>
       <c r="P5">
-        <v>0.7257802814881636</v>
+        <v>0.7193072771157977</v>
       </c>
       <c r="Q5">
-        <v>39.24052857416536</v>
+        <v>39.79208019813978</v>
       </c>
       <c r="R5">
         <v>-89.99999999999638</v>
       </c>
       <c r="S5">
-        <v>145.4163851967612</v>
+        <v>145.7654013218176</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7919,22 +7919,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.7696154299170926</v>
+        <v>0.7691699432153671</v>
       </c>
       <c r="O6">
-        <v>0.8999999761574552</v>
+        <v>0.8999999761574192</v>
       </c>
       <c r="P6">
-        <v>0.7862743000218492</v>
+        <v>0.7803474434319086</v>
       </c>
       <c r="Q6">
-        <v>34.47158198599157</v>
+        <v>34.92729804409172</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999638</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S6">
-        <v>143.7980514675988</v>
+        <v>143.9141574520902</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -7981,22 +7981,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.7696154299461612</v>
+        <v>0.7691699432469293</v>
       </c>
       <c r="O7">
-        <v>0.8999999761574552</v>
+        <v>0.8999999761574192</v>
       </c>
       <c r="P7">
-        <v>0.7862742999916136</v>
+        <v>0.7803474434025236</v>
       </c>
       <c r="Q7">
-        <v>34.47158198913591</v>
+        <v>34.9272980472155</v>
       </c>
       <c r="R7">
-        <v>-89.99999999999638</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S7">
-        <v>143.7980514706162</v>
+        <v>143.9141574552833</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -8007,7 +8007,7 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>25.27620911770471</v>
+        <v>25.87439961861448</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -8016,7 +8016,7 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>5.83729054226244</v>
+        <v>5.975436723011753</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -8025,43 +8025,43 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0.004540640357537415</v>
+        <v>0.003557604122208396</v>
       </c>
       <c r="I8">
-        <v>0.007926334487990933</v>
+        <v>0.007673124089798526</v>
       </c>
       <c r="J8">
-        <v>0.002093407521777885</v>
+        <v>0.002093407521777895</v>
       </c>
       <c r="K8">
-        <v>0.007573622492710872</v>
+        <v>0.007573622492710861</v>
       </c>
       <c r="L8">
-        <v>0.002093407521783731</v>
+        <v>0.002093407521783739</v>
       </c>
       <c r="M8">
-        <v>0.007573622492710515</v>
+        <v>0.007573622492710481</v>
       </c>
       <c r="N8">
-        <v>0.4947446922650668</v>
+        <v>0.5010416015924202</v>
       </c>
       <c r="O8">
-        <v>0.8999999761574734</v>
+        <v>0.8999999761574413</v>
       </c>
       <c r="P8">
-        <v>0.5716867624688216</v>
+        <v>0.5510127760503385</v>
       </c>
       <c r="Q8">
-        <v>54.82746094553925</v>
+        <v>57.12287474676723</v>
       </c>
       <c r="R8">
         <v>-89.99999999999655</v>
       </c>
       <c r="S8">
-        <v>119.9016405334565</v>
+        <v>119.5780865591122</v>
       </c>
       <c r="T8">
-        <v>25.2762091177047</v>
+        <v>25.87439961861448</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -8105,22 +8105,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.7696154299461612</v>
+        <v>0.7691699432469293</v>
       </c>
       <c r="O9">
-        <v>0.8999999761574552</v>
+        <v>0.8999999761574192</v>
       </c>
       <c r="P9">
-        <v>0.7862742999916136</v>
+        <v>0.7803474434025236</v>
       </c>
       <c r="Q9">
-        <v>34.47158198913591</v>
+        <v>34.9272980472155</v>
       </c>
       <c r="R9">
-        <v>-89.99999999999638</v>
+        <v>-89.99999999999636</v>
       </c>
       <c r="S9">
-        <v>143.7980514706162</v>
+        <v>143.9141574552833</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -8239,22 +8239,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9498470387606186</v>
+        <v>0.9498470318593625</v>
       </c>
       <c r="O2">
         <v>0.9499999880790705</v>
       </c>
       <c r="P2">
-        <v>0.9499451250780433</v>
+        <v>0.9499451192952771</v>
       </c>
       <c r="Q2">
-        <v>29.9984954470181</v>
+        <v>29.9984956094987</v>
       </c>
       <c r="R2">
         <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>149.9912586024636</v>
+        <v>149.99125832317</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -8301,22 +8301,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9498213780766108</v>
+        <v>0.9498213707316043</v>
       </c>
       <c r="O3">
         <v>0.9499999880790705</v>
       </c>
       <c r="P3">
-        <v>0.949910499086916</v>
+        <v>0.9499104916446365</v>
       </c>
       <c r="Q3">
-        <v>30.00001369175634</v>
+        <v>30.00001395438626</v>
       </c>
       <c r="R3">
         <v>-89.99999999999635</v>
       </c>
       <c r="S3">
-        <v>149.9906769588548</v>
+        <v>149.9906767064099</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -8363,22 +8363,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9498213780766349</v>
+        <v>0.9498213707316285</v>
       </c>
       <c r="O4">
         <v>0.9499999880790705</v>
       </c>
       <c r="P4">
-        <v>0.9499104990869227</v>
+        <v>0.9499104916446431</v>
       </c>
       <c r="Q4">
-        <v>30.00001369175671</v>
+        <v>30.00001395438663</v>
       </c>
       <c r="R4">
         <v>-89.99999999999635</v>
       </c>
       <c r="S4">
-        <v>149.9906769588562</v>
+        <v>149.9906767064114</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -8425,22 +8425,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9497827471842477</v>
+        <v>0.9497827399164462</v>
       </c>
       <c r="O5">
         <v>0.9499999880790705</v>
       </c>
       <c r="P5">
-        <v>0.9498318458294897</v>
+        <v>0.9498318351694643</v>
       </c>
       <c r="Q5">
-        <v>30.00414691876789</v>
+        <v>30.00414740822652</v>
       </c>
       <c r="R5">
         <v>-89.99999999999635</v>
       </c>
       <c r="S5">
-        <v>149.9907244698038</v>
+        <v>149.9907243346969</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -8487,22 +8487,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9498213780766349</v>
+        <v>0.9498213707316285</v>
       </c>
       <c r="O6">
         <v>0.9499999880790705</v>
       </c>
       <c r="P6">
-        <v>0.9499104990869227</v>
+        <v>0.9499104916446431</v>
       </c>
       <c r="Q6">
-        <v>30.00001369175671</v>
+        <v>30.00001395438663</v>
       </c>
       <c r="R6">
         <v>-89.99999999999635</v>
       </c>
       <c r="S6">
-        <v>149.9906769588562</v>
+        <v>149.9906767064114</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -8549,22 +8549,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.9498213780766415</v>
+        <v>0.9498213707316348</v>
       </c>
       <c r="O7">
         <v>0.9499999880790705</v>
       </c>
       <c r="P7">
-        <v>0.9499104990868719</v>
+        <v>0.9499104916445922</v>
       </c>
       <c r="Q7">
-        <v>30.00001369176048</v>
+        <v>30.0000139543904</v>
       </c>
       <c r="R7">
         <v>-89.99999999999635</v>
       </c>
       <c r="S7">
-        <v>149.9906769588585</v>
+        <v>149.9906767064136</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -8575,7 +8575,7 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>0.0309940118864007</v>
+        <v>0.03099528742527187</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -8584,7 +8584,7 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0.007157760549010904</v>
+        <v>0.007158055122099547</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -8593,43 +8593,43 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0.004540640357537415</v>
+        <v>0.003557604122208396</v>
       </c>
       <c r="I8">
-        <v>0.007926334487990933</v>
+        <v>0.007673124089798526</v>
       </c>
       <c r="J8">
-        <v>0.002093407521777885</v>
+        <v>0.002093407521777895</v>
       </c>
       <c r="K8">
-        <v>0.007573622492710872</v>
+        <v>0.007573622492710861</v>
       </c>
       <c r="L8">
-        <v>0.002093407521783731</v>
+        <v>0.002093407521783739</v>
       </c>
       <c r="M8">
-        <v>0.007573622492710515</v>
+        <v>0.007573622492710481</v>
       </c>
       <c r="N8">
-        <v>0.9493911618129558</v>
+        <v>0.9493911368810545</v>
       </c>
       <c r="O8">
         <v>0.9499999880790705</v>
       </c>
       <c r="P8">
-        <v>0.9496913157193835</v>
+        <v>0.9496912902551808</v>
       </c>
       <c r="Q8">
-        <v>30.00030691030953</v>
+        <v>30.00030781665616</v>
       </c>
       <c r="R8">
         <v>-89.99999999999635</v>
       </c>
       <c r="S8">
-        <v>149.9683433670526</v>
+        <v>149.9683425165801</v>
       </c>
       <c r="T8">
-        <v>0.0309940118864007</v>
+        <v>0.03099528742527187</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -8673,22 +8673,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.9498213780766415</v>
+        <v>0.9498213707316348</v>
       </c>
       <c r="O9">
         <v>0.9499999880790705</v>
       </c>
       <c r="P9">
-        <v>0.9499104990868719</v>
+        <v>0.9499104916445922</v>
       </c>
       <c r="Q9">
-        <v>30.00001369176048</v>
+        <v>30.0000139543904</v>
       </c>
       <c r="R9">
         <v>-89.99999999999635</v>
       </c>
       <c r="S9">
-        <v>149.9906769588585</v>
+        <v>149.9906767064136</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -8807,22 +8807,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8998550768058391</v>
+        <v>0.8998550702678071</v>
       </c>
       <c r="O2">
         <v>0.8999999761581415</v>
       </c>
       <c r="P2">
-        <v>0.899948000684209</v>
+        <v>0.8999479952057989</v>
       </c>
       <c r="Q2">
-        <v>29.9984954470181</v>
+        <v>29.99849560949869</v>
       </c>
       <c r="R2">
         <v>-89.99999999999635</v>
       </c>
       <c r="S2">
-        <v>149.9912586024636</v>
+        <v>149.99125832317</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -8869,22 +8869,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8998307666844864</v>
+        <v>0.8998307597260592</v>
       </c>
       <c r="O3">
         <v>0.8999999761581415</v>
       </c>
       <c r="P3">
-        <v>0.8999151971141246</v>
+        <v>0.8999151900635441</v>
       </c>
       <c r="Q3">
-        <v>30.00001369175633</v>
+        <v>30.00001395438625</v>
       </c>
       <c r="R3">
         <v>-89.99999999999635</v>
       </c>
       <c r="S3">
-        <v>149.9906769588548</v>
+        <v>149.9906767064099</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -8931,22 +8931,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8998307666845092</v>
+        <v>0.8998307597260821</v>
       </c>
       <c r="O4">
         <v>0.8999999761581415</v>
       </c>
       <c r="P4">
-        <v>0.8999151971141309</v>
+        <v>0.8999151900635504</v>
       </c>
       <c r="Q4">
-        <v>30.00001369175671</v>
+        <v>30.00001395438663</v>
       </c>
       <c r="R4">
         <v>-89.99999999999635</v>
       </c>
       <c r="S4">
-        <v>149.9906769588563</v>
+        <v>149.9906767064114</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -8993,22 +8993,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8997941689974946</v>
+        <v>0.8997941621122091</v>
       </c>
       <c r="O5">
         <v>0.8999999761581415</v>
       </c>
       <c r="P5">
-        <v>0.8998406835028651</v>
+        <v>0.8998406734038936</v>
       </c>
       <c r="Q5">
-        <v>30.00414691876789</v>
+        <v>30.00414740822652</v>
       </c>
       <c r="R5">
         <v>-89.99999999999635</v>
       </c>
       <c r="S5">
-        <v>149.9907244698038</v>
+        <v>149.9907243346969</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -9055,22 +9055,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8998307666845092</v>
+        <v>0.8998307597260821</v>
       </c>
       <c r="O6">
         <v>0.8999999761581415</v>
       </c>
       <c r="P6">
-        <v>0.8999151971141309</v>
+        <v>0.8999151900635504</v>
       </c>
       <c r="Q6">
-        <v>30.00001369175671</v>
+        <v>30.00001395438663</v>
       </c>
       <c r="R6">
         <v>-89.99999999999635</v>
       </c>
       <c r="S6">
-        <v>149.9906769588563</v>
+        <v>149.9906767064114</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -9117,22 +9117,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.8998307666845153</v>
+        <v>0.8998307597260882</v>
       </c>
       <c r="O7">
         <v>0.8999999761581415</v>
       </c>
       <c r="P7">
-        <v>0.8999151971140827</v>
+        <v>0.8999151900635021</v>
       </c>
       <c r="Q7">
-        <v>30.00001369176048</v>
+        <v>30.00001395439041</v>
       </c>
       <c r="R7">
         <v>-89.99999999999635</v>
       </c>
       <c r="S7">
-        <v>149.9906769588585</v>
+        <v>149.9906767064136</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -9143,7 +9143,7 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>0.02936274769351267</v>
+        <v>0.02936395609874219</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -9152,7 +9152,7 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0.006781036215043953</v>
+        <v>0.006781315284281933</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -9161,43 +9161,43 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0.004540640357537415</v>
+        <v>0.003557604122208396</v>
       </c>
       <c r="I8">
-        <v>0.007926334487990933</v>
+        <v>0.007673124089798526</v>
       </c>
       <c r="J8">
-        <v>0.002093407521777885</v>
+        <v>0.002093407521777895</v>
       </c>
       <c r="K8">
-        <v>0.007573622492710872</v>
+        <v>0.007573622492710861</v>
       </c>
       <c r="L8">
-        <v>0.002093407521783731</v>
+        <v>0.002093407521783739</v>
       </c>
       <c r="M8">
-        <v>0.007573622492710515</v>
+        <v>0.007573622492710481</v>
       </c>
       <c r="N8">
-        <v>0.899423193387759</v>
+        <v>0.8994231697680634</v>
       </c>
       <c r="O8">
         <v>0.8999999761581415</v>
       </c>
       <c r="P8">
-        <v>0.8997075497161996</v>
+        <v>0.8997075255922183</v>
       </c>
       <c r="Q8">
-        <v>30.00030691030953</v>
+        <v>30.00030781665615</v>
       </c>
       <c r="R8">
         <v>-89.99999999999635</v>
       </c>
       <c r="S8">
-        <v>149.9683433670526</v>
+        <v>149.9683425165802</v>
       </c>
       <c r="T8">
-        <v>0.02936274769351266</v>
+        <v>0.02936395609874219</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -9241,22 +9241,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.8998307666845153</v>
+        <v>0.8998307597260882</v>
       </c>
       <c r="O9">
         <v>0.8999999761581415</v>
       </c>
       <c r="P9">
-        <v>0.8999151971140827</v>
+        <v>0.8999151900635021</v>
       </c>
       <c r="Q9">
-        <v>30.00001369176048</v>
+        <v>30.00001395439041</v>
       </c>
       <c r="R9">
         <v>-89.99999999999635</v>
       </c>
       <c r="S9">
-        <v>149.9906769588585</v>
+        <v>149.9906767064136</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -9375,22 +9375,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9353714700489314</v>
+        <v>0.933689583918526</v>
       </c>
       <c r="O2">
-        <v>0.7956426181704875</v>
+        <v>0.7956426181704876</v>
       </c>
       <c r="P2">
-        <v>0.9255163760584846</v>
+        <v>0.9220037576344834</v>
       </c>
       <c r="Q2">
-        <v>24.24346529430613</v>
+        <v>24.43736569398093</v>
       </c>
       <c r="R2">
-        <v>-91.70926262353147</v>
+        <v>-91.70926262353198</v>
       </c>
       <c r="S2">
-        <v>153.6211449756103</v>
+        <v>153.6646736310186</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -9437,22 +9437,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9085266883069345</v>
+        <v>0.9069155796259121</v>
       </c>
       <c r="O3">
-        <v>0.7558344349754622</v>
+        <v>0.755834434975461</v>
       </c>
       <c r="P3">
-        <v>0.9149352327802396</v>
+        <v>0.9110160049846632</v>
       </c>
       <c r="Q3">
-        <v>23.99801258010643</v>
+        <v>24.23729677444335</v>
       </c>
       <c r="R3">
-        <v>-90.04726476646847</v>
+        <v>-90.04726476646906</v>
       </c>
       <c r="S3">
-        <v>155.0232464148777</v>
+        <v>155.1027853503658</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -9499,22 +9499,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9085266883126666</v>
+        <v>0.9069155796319408</v>
       </c>
       <c r="O4">
-        <v>0.7558344349961416</v>
+        <v>0.75583443499614</v>
       </c>
       <c r="P4">
-        <v>0.9149352327926653</v>
+        <v>0.9110160049974063</v>
       </c>
       <c r="Q4">
-        <v>23.99801258089187</v>
+        <v>24.23729677521531</v>
       </c>
       <c r="R4">
-        <v>-90.04726476568747</v>
+        <v>-90.04726476568806</v>
       </c>
       <c r="S4">
-        <v>155.0232464147581</v>
+        <v>155.1027853502476</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -9561,22 +9561,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8607616714421723</v>
+        <v>0.8597964415077499</v>
       </c>
       <c r="O5">
-        <v>0.7084903204193633</v>
+        <v>0.7084903204193584</v>
       </c>
       <c r="P5">
-        <v>0.9143382498547309</v>
+        <v>0.91015850130342</v>
       </c>
       <c r="Q5">
-        <v>24.78035573355064</v>
+        <v>25.10101464729583</v>
       </c>
       <c r="R5">
-        <v>-84.70550824735928</v>
+        <v>-84.70550824735987</v>
       </c>
       <c r="S5">
-        <v>157.8532572387867</v>
+        <v>158.0151207851497</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -9623,22 +9623,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9085266883126666</v>
+        <v>0.9069155796319408</v>
       </c>
       <c r="O6">
-        <v>0.7558344349961416</v>
+        <v>0.75583443499614</v>
       </c>
       <c r="P6">
-        <v>0.9149352327926653</v>
+        <v>0.9110160049974063</v>
       </c>
       <c r="Q6">
-        <v>23.99801258089187</v>
+        <v>24.23729677521531</v>
       </c>
       <c r="R6">
-        <v>-90.04726476568747</v>
+        <v>-90.04726476568806</v>
       </c>
       <c r="S6">
-        <v>155.0232464147581</v>
+        <v>155.1027853502476</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -9685,22 +9685,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.9085266882806063</v>
+        <v>0.9069155796014042</v>
       </c>
       <c r="O7">
-        <v>0.7558344350057106</v>
+        <v>0.7558344350057091</v>
       </c>
       <c r="P7">
-        <v>0.9149352328277117</v>
+        <v>0.9110160050330638</v>
       </c>
       <c r="Q7">
-        <v>23.99801258397775</v>
+        <v>24.23729677834085</v>
       </c>
       <c r="R7">
-        <v>-90.04726475824997</v>
+        <v>-90.04726475825055</v>
       </c>
       <c r="S7">
-        <v>155.0232464173012</v>
+        <v>155.102785352878</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -9714,58 +9714,58 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>34.50160698312441</v>
+        <v>34.28852085873783</v>
       </c>
       <c r="D8">
-        <v>31.63629146646118</v>
+        <v>32.41498098946658</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>7.967804950402165</v>
+        <v>7.91859481715881</v>
       </c>
       <c r="G8">
-        <v>7.306088666598334</v>
+        <v>7.485919311566941</v>
       </c>
       <c r="H8">
-        <v>0.002657050495199304</v>
+        <v>0.002145052455584837</v>
       </c>
       <c r="I8">
-        <v>0.007445544226858886</v>
+        <v>0.007192333827821748</v>
       </c>
       <c r="J8">
-        <v>0.001382566736038376</v>
+        <v>0.001382566736038385</v>
       </c>
       <c r="K8">
-        <v>0.007090446173215316</v>
+        <v>0.007090446173215331</v>
       </c>
       <c r="L8">
-        <v>0.001382566736026977</v>
+        <v>0.001382566736026993</v>
       </c>
       <c r="M8">
         <v>0.007090446173195246</v>
       </c>
       <c r="N8">
-        <v>0.6256703197249706</v>
+        <v>0.6145277086463387</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>0.6256703197244319</v>
+        <v>0.6145277086457865</v>
       </c>
       <c r="Q8">
-        <v>-2.696337730011683</v>
+        <v>-1.810001889179975</v>
       </c>
       <c r="R8">
         <v>0</v>
       </c>
       <c r="S8">
-        <v>177.3036622700789</v>
+        <v>178.1899981109172</v>
       </c>
       <c r="T8">
-        <v>31.65769423633974</v>
+        <v>32.7512636470548</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -9809,22 +9809,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.9085266882806063</v>
+        <v>0.9069155796014042</v>
       </c>
       <c r="O9">
-        <v>0.7558344350057106</v>
+        <v>0.7558344350057092</v>
       </c>
       <c r="P9">
-        <v>0.9149352328277118</v>
+        <v>0.9110160050330638</v>
       </c>
       <c r="Q9">
-        <v>23.99801258397775</v>
+        <v>24.23729677834085</v>
       </c>
       <c r="R9">
-        <v>-90.04726475824997</v>
+        <v>-90.04726475825055</v>
       </c>
       <c r="S9">
-        <v>155.0232464173012</v>
+        <v>155.102785352878</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -9943,22 +9943,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.983061245027338</v>
+        <v>0.9814468451309729</v>
       </c>
       <c r="O2">
-        <v>0.8416889876470159</v>
+        <v>0.8416889876470154</v>
       </c>
       <c r="P2">
-        <v>0.9735142739940978</v>
+        <v>0.9700541997834243</v>
       </c>
       <c r="Q2">
-        <v>24.47495348457333</v>
+        <v>24.65837777653349</v>
       </c>
       <c r="R2">
-        <v>-91.58959683085547</v>
+        <v>-91.58959683085607</v>
       </c>
       <c r="S2">
-        <v>153.5192430317697</v>
+        <v>153.5618545344529</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -10005,22 +10005,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9557913694830624</v>
+        <v>0.9542571511456335</v>
       </c>
       <c r="O3">
-        <v>0.8013810488005501</v>
+        <v>0.8013810488005477</v>
       </c>
       <c r="P3">
-        <v>0.9627603585022432</v>
+        <v>0.958902854574527</v>
       </c>
       <c r="Q3">
-        <v>24.25207582423001</v>
+        <v>24.47789446457468</v>
       </c>
       <c r="R3">
-        <v>-89.9839149902984</v>
+        <v>-89.9839149902991</v>
       </c>
       <c r="S3">
-        <v>154.874661732962</v>
+        <v>154.9510573124951</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -10067,22 +10067,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9557913694889899</v>
+        <v>0.9542571511518489</v>
       </c>
       <c r="O4">
-        <v>0.8013810488215836</v>
+        <v>0.8013810488215812</v>
       </c>
       <c r="P4">
-        <v>0.9627603585148792</v>
+        <v>0.9589028545874767</v>
       </c>
       <c r="Q4">
-        <v>24.25207582498437</v>
+        <v>24.47789446531612</v>
       </c>
       <c r="R4">
-        <v>-89.98391498955661</v>
+        <v>-89.98391498955729</v>
       </c>
       <c r="S4">
-        <v>154.8746617328465</v>
+        <v>154.9510573123808</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -10129,22 +10129,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9074401943528634</v>
+        <v>0.9065577812382374</v>
       </c>
       <c r="O5">
-        <v>0.7534627028494136</v>
+        <v>0.753462702849407</v>
       </c>
       <c r="P5">
-        <v>0.9621086921529644</v>
+        <v>0.9579999135571177</v>
       </c>
       <c r="Q5">
-        <v>25.03212925298871</v>
+        <v>25.3331090493723</v>
       </c>
       <c r="R5">
-        <v>-84.87011703383217</v>
+        <v>-84.87011703383287</v>
       </c>
       <c r="S5">
-        <v>157.6095508713444</v>
+        <v>157.7628414261446</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -10191,22 +10191,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9557913694889899</v>
+        <v>0.9542571511518489</v>
       </c>
       <c r="O6">
-        <v>0.8013810488215836</v>
+        <v>0.8013810488215812</v>
       </c>
       <c r="P6">
-        <v>0.9627603585148792</v>
+        <v>0.9589028545874766</v>
       </c>
       <c r="Q6">
-        <v>24.25207582498437</v>
+        <v>24.47789446531612</v>
       </c>
       <c r="R6">
-        <v>-89.98391498955662</v>
+        <v>-89.98391498955729</v>
       </c>
       <c r="S6">
-        <v>154.8746617328465</v>
+        <v>154.9510573123808</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -10253,22 +10253,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.9557913694553757</v>
+        <v>0.9542571511198105</v>
       </c>
       <c r="O7">
-        <v>0.801381048832175</v>
+        <v>0.8013810488321728</v>
       </c>
       <c r="P7">
-        <v>0.9627603585522092</v>
+        <v>0.9589028546254481</v>
       </c>
       <c r="Q7">
-        <v>24.25207582812013</v>
+        <v>24.47789446848892</v>
       </c>
       <c r="R7">
-        <v>-89.98391498209951</v>
+        <v>-89.98391498210019</v>
       </c>
       <c r="S7">
-        <v>154.8746617354215</v>
+        <v>154.9510573150409</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -10282,58 +10282,58 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>35.00464973485094</v>
+        <v>34.78941197223003</v>
       </c>
       <c r="D8">
-        <v>32.17128742405514</v>
+        <v>32.94151230962335</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>8.083977699382555</v>
+        <v>8.034270666566279</v>
       </c>
       <c r="G8">
-        <v>7.429640692492295</v>
+        <v>7.607516513150593</v>
       </c>
       <c r="H8">
-        <v>0.002680261932313766</v>
+        <v>0.00216826389269289</v>
       </c>
       <c r="I8">
-        <v>0.007676495104230187</v>
+        <v>0.007423284705210115</v>
       </c>
       <c r="J8">
         <v>0.001405778171205794</v>
       </c>
       <c r="K8">
-        <v>0.007321397045619365</v>
+        <v>0.007321397045619378</v>
       </c>
       <c r="L8">
-        <v>0.001405778171188655</v>
+        <v>0.001405778171188657</v>
       </c>
       <c r="M8">
-        <v>0.007321397045589348</v>
+        <v>0.007321397045589349</v>
       </c>
       <c r="N8">
-        <v>0.6546894544212909</v>
+        <v>0.6434269347582597</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>0.6546894544206018</v>
+        <v>0.6434269347575432</v>
       </c>
       <c r="Q8">
-        <v>-2.631021148253061</v>
+        <v>-1.760052630582366</v>
       </c>
       <c r="R8">
         <v>0</v>
       </c>
       <c r="S8">
-        <v>177.3689788518078</v>
+        <v>178.2399473694819</v>
       </c>
       <c r="T8">
-        <v>32.20727220068468</v>
+        <v>33.28012537062521</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -10377,22 +10377,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.9557913694553757</v>
+        <v>0.9542571511198105</v>
       </c>
       <c r="O9">
-        <v>0.801381048832175</v>
+        <v>0.8013810488321726</v>
       </c>
       <c r="P9">
-        <v>0.9627603585522092</v>
+        <v>0.958902854625448</v>
       </c>
       <c r="Q9">
-        <v>24.25207582812013</v>
+        <v>24.47789446848893</v>
       </c>
       <c r="R9">
-        <v>-89.98391498209951</v>
+        <v>-89.98391498210019</v>
       </c>
       <c r="S9">
-        <v>154.8746617354215</v>
+        <v>154.9510573150409</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -10511,22 +10511,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.049946573961266</v>
+        <v>1.049946569960974</v>
       </c>
       <c r="O2">
         <v>1.04979777117332</v>
       </c>
       <c r="P2">
-        <v>1.049851162303442</v>
+        <v>1.049851159726485</v>
       </c>
       <c r="Q2">
-        <v>29.99230608147668</v>
+        <v>29.99230611780087</v>
       </c>
       <c r="R2">
         <v>-90.00901840975767</v>
       </c>
       <c r="S2">
-        <v>149.9986768177257</v>
+        <v>149.9986766468374</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -10573,22 +10573,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.04992412623156</v>
+        <v>1.049924121719864</v>
       </c>
       <c r="O3">
         <v>1.049751189443895</v>
       </c>
       <c r="P3">
-        <v>1.049827032356231</v>
+        <v>1.04982702907866</v>
       </c>
       <c r="Q3">
-        <v>29.99149258646241</v>
+        <v>29.99149265081624</v>
       </c>
       <c r="R3">
         <v>-90.00917769029607</v>
       </c>
       <c r="S3">
-        <v>149.9993312548786</v>
+        <v>149.9993310738397</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -10635,22 +10635,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.04992412623156</v>
+        <v>1.049924121719864</v>
       </c>
       <c r="O4">
         <v>1.049751189443906</v>
       </c>
       <c r="P4">
-        <v>1.049827032356243</v>
+        <v>1.049827029078672</v>
       </c>
       <c r="Q4">
-        <v>29.99149258646315</v>
+        <v>29.99149265081698</v>
       </c>
       <c r="R4">
         <v>-90.00917769029496</v>
       </c>
       <c r="S4">
-        <v>149.999331254879</v>
+        <v>149.9993310738401</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -10697,22 +10697,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.049876145779686</v>
+        <v>1.049876140762639</v>
       </c>
       <c r="O5">
         <v>1.049670921668675</v>
       </c>
       <c r="P5">
-        <v>1.049794754237893</v>
+        <v>1.049794749655149</v>
       </c>
       <c r="Q5">
-        <v>29.99096963107212</v>
+        <v>29.99096976174622</v>
       </c>
       <c r="R5">
         <v>-90.00769394041889</v>
       </c>
       <c r="S5">
-        <v>150.0013379032206</v>
+        <v>150.0013377314722</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -10759,22 +10759,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>1.04992412623156</v>
+        <v>1.049924121719864</v>
       </c>
       <c r="O6">
         <v>1.049751189443906</v>
       </c>
       <c r="P6">
-        <v>1.049827032356243</v>
+        <v>1.049827029078672</v>
       </c>
       <c r="Q6">
-        <v>29.99149258646315</v>
+        <v>29.99149265081698</v>
       </c>
       <c r="R6">
         <v>-90.00917769029496</v>
       </c>
       <c r="S6">
-        <v>149.999331254879</v>
+        <v>149.9993310738401</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -10821,22 +10821,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>1.049924126231511</v>
+        <v>1.049924121719815</v>
       </c>
       <c r="O7">
         <v>1.049751189443858</v>
       </c>
       <c r="P7">
-        <v>1.049827032356245</v>
+        <v>1.049827029078674</v>
       </c>
       <c r="Q7">
-        <v>29.99149258646481</v>
+        <v>29.99149265081865</v>
       </c>
       <c r="R7">
         <v>-90.00917769029013</v>
       </c>
       <c r="S7">
-        <v>149.9993312548822</v>
+        <v>149.9993310738433</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -10850,58 +10850,58 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0.03426379795180608</v>
+        <v>0.03426397831682162</v>
       </c>
       <c r="D8">
-        <v>0.03426197925114097</v>
+        <v>0.03426267177088742</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>0.007912885306284853</v>
+        <v>0.007912926959801583</v>
       </c>
       <c r="G8">
-        <v>0.007912465295351164</v>
+        <v>0.007912625225938361</v>
       </c>
       <c r="H8">
-        <v>0.002657050495199304</v>
+        <v>0.002145052455584837</v>
       </c>
       <c r="I8">
-        <v>0.007445544226858886</v>
+        <v>0.007192333827821748</v>
       </c>
       <c r="J8">
-        <v>0.001382566736038376</v>
+        <v>0.001382566736038385</v>
       </c>
       <c r="K8">
-        <v>0.007090446173215316</v>
+        <v>0.007090446173215331</v>
       </c>
       <c r="L8">
-        <v>0.001382566736026977</v>
+        <v>0.001382566736026993</v>
       </c>
       <c r="M8">
         <v>0.007090446173195246</v>
       </c>
       <c r="N8">
-        <v>1.049728225135845</v>
+        <v>1.049728209039105</v>
       </c>
       <c r="O8">
         <v>1.049110868568147</v>
       </c>
       <c r="P8">
-        <v>1.049382639756281</v>
+        <v>1.049382628032563</v>
       </c>
       <c r="Q8">
-        <v>29.96965928879356</v>
+        <v>29.96965952006926</v>
       </c>
       <c r="R8">
-        <v>-90.03267605016319</v>
+        <v>-90.03267605016318</v>
       </c>
       <c r="S8">
-        <v>149.9976834001723</v>
+        <v>149.9976827550339</v>
       </c>
       <c r="T8">
-        <v>0.03426010030717948</v>
+        <v>0.03426184616206149</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -10945,22 +10945,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>1.049924126231511</v>
+        <v>1.049924121719815</v>
       </c>
       <c r="O9">
         <v>1.049751189443858</v>
       </c>
       <c r="P9">
-        <v>1.049827032356245</v>
+        <v>1.049827029078674</v>
       </c>
       <c r="Q9">
-        <v>29.99149258646481</v>
+        <v>29.99149265081865</v>
       </c>
       <c r="R9">
         <v>-90.00917769029013</v>
       </c>
       <c r="S9">
-        <v>149.9993312548822</v>
+        <v>149.9993310738433</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -11079,22 +11079,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.099944102013146</v>
+        <v>1.099944097822605</v>
       </c>
       <c r="O2">
         <v>1.09978821680106</v>
       </c>
       <c r="P2">
-        <v>1.099844152013116</v>
+        <v>1.099844149313447</v>
       </c>
       <c r="Q2">
-        <v>29.99230633735992</v>
+        <v>29.99230637369132</v>
       </c>
       <c r="R2">
         <v>-90.00901795173628</v>
       </c>
       <c r="S2">
-        <v>149.9986770197513</v>
+        <v>149.9986768488775</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -11141,22 +11141,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.099920585615784</v>
+        <v>1.099920580889536</v>
       </c>
       <c r="O3">
         <v>1.099739418067158</v>
       </c>
       <c r="P3">
-        <v>1.099818873921908</v>
+        <v>1.099818870488292</v>
       </c>
       <c r="Q3">
-        <v>29.99149288842658</v>
+        <v>29.99149295278737</v>
       </c>
       <c r="R3">
         <v>-90.00917717547475</v>
       </c>
       <c r="S3">
-        <v>149.9993314675916</v>
+        <v>149.9993312865693</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -11203,22 +11203,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.099920585615783</v>
+        <v>1.099920580889536</v>
       </c>
       <c r="O4">
         <v>1.09973941806717</v>
       </c>
       <c r="P4">
-        <v>1.09981887392192</v>
+        <v>1.099818870488305</v>
       </c>
       <c r="Q4">
-        <v>29.99149288842733</v>
+        <v>29.9914929527881</v>
       </c>
       <c r="R4">
         <v>-90.00917717547362</v>
       </c>
       <c r="S4">
-        <v>149.9993314675919</v>
+        <v>149.9993312865696</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -11265,22 +11265,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.099870321445811</v>
+        <v>1.099870316190228</v>
       </c>
       <c r="O5">
         <v>1.099655330738635</v>
       </c>
       <c r="P5">
-        <v>1.099785060406101</v>
+        <v>1.099785055605238</v>
       </c>
       <c r="Q5">
-        <v>29.99097000064921</v>
+        <v>29.99097013132804</v>
       </c>
       <c r="R5">
         <v>-90.00769337238869</v>
       </c>
       <c r="S5">
-        <v>150.001338101485</v>
+        <v>150.0013379297557</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -11327,22 +11327,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>1.099920585615783</v>
+        <v>1.099920580889536</v>
       </c>
       <c r="O6">
         <v>1.09973941806717</v>
       </c>
       <c r="P6">
-        <v>1.09981887392192</v>
+        <v>1.099818870488305</v>
       </c>
       <c r="Q6">
-        <v>29.99149288842733</v>
+        <v>29.9914929527881</v>
       </c>
       <c r="R6">
         <v>-90.00917717547362</v>
       </c>
       <c r="S6">
-        <v>149.9993314675919</v>
+        <v>149.9993312865696</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -11389,22 +11389,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>1.099920585615729</v>
+        <v>1.099920580889482</v>
       </c>
       <c r="O7">
         <v>1.099739418067118</v>
       </c>
       <c r="P7">
-        <v>1.099818873921922</v>
+        <v>1.099818870488306</v>
       </c>
       <c r="Q7">
-        <v>29.99149288842907</v>
+        <v>29.99149295278985</v>
       </c>
       <c r="R7">
         <v>-90.00917717546857</v>
       </c>
       <c r="S7">
-        <v>149.9993314675953</v>
+        <v>149.999331286573</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -11418,58 +11418,58 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0.03589449787030109</v>
+        <v>0.0358946867949031</v>
       </c>
       <c r="D8">
-        <v>0.03589259259157075</v>
+        <v>0.03589331806485223</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>0.008289479326660781</v>
+        <v>0.008289522956929361</v>
       </c>
       <c r="G8">
-        <v>0.008289039321379086</v>
+        <v>0.008289206862259323</v>
       </c>
       <c r="H8">
-        <v>0.002680261932313766</v>
+        <v>0.00216826389269289</v>
       </c>
       <c r="I8">
-        <v>0.007676495104230187</v>
+        <v>0.007423284705210115</v>
       </c>
       <c r="J8">
         <v>0.001405778171205794</v>
       </c>
       <c r="K8">
-        <v>0.007321397045619365</v>
+        <v>0.007321397045619378</v>
       </c>
       <c r="L8">
-        <v>0.001405778171188655</v>
+        <v>0.001405778171188657</v>
       </c>
       <c r="M8">
-        <v>0.007321397045589348</v>
+        <v>0.007321397045589349</v>
       </c>
       <c r="N8">
-        <v>1.099707976714867</v>
+        <v>1.099707959299923</v>
       </c>
       <c r="O8">
         <v>1.099040679649232</v>
       </c>
       <c r="P8">
-        <v>1.099332772474043</v>
+        <v>1.099332759835952</v>
       </c>
       <c r="Q8">
-        <v>29.96864547304403</v>
+        <v>29.96864570912545</v>
       </c>
       <c r="R8">
         <v>-90.03386444142927</v>
       </c>
       <c r="S8">
-        <v>149.9975100891732</v>
+        <v>149.9975094215432</v>
       </c>
       <c r="T8">
-        <v>0.03589062434315304</v>
+        <v>0.03589245322833131</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -11513,22 +11513,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>1.099920585615729</v>
+        <v>1.099920580889482</v>
       </c>
       <c r="O9">
         <v>1.099739418067118</v>
       </c>
       <c r="P9">
-        <v>1.099818873921922</v>
+        <v>1.099818870488306</v>
       </c>
       <c r="Q9">
-        <v>29.99149288842907</v>
+        <v>29.99149295278985</v>
       </c>
       <c r="R9">
         <v>-90.00917717546857</v>
       </c>
       <c r="S9">
-        <v>149.9993314675953</v>
+        <v>149.999331286573</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -11647,22 +11647,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8518937268494307</v>
+        <v>0.849065914616782</v>
       </c>
       <c r="O2">
-        <v>0.7128571052617145</v>
+        <v>0.7128571052617519</v>
       </c>
       <c r="P2">
-        <v>0.8329712730645756</v>
+        <v>0.8277989130444918</v>
       </c>
       <c r="Q2">
-        <v>23.11067999091066</v>
+        <v>23.40553628518304</v>
       </c>
       <c r="R2">
-        <v>-93.28996606057379</v>
+        <v>-93.28996606057261</v>
       </c>
       <c r="S2">
-        <v>153.0659392340804</v>
+        <v>153.1095271361261</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -11709,22 +11709,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8180647983928183</v>
+        <v>0.8156809317535487</v>
       </c>
       <c r="O3">
-        <v>0.6713200058613498</v>
+        <v>0.671320005861391</v>
       </c>
       <c r="P3">
-        <v>0.8270854595226502</v>
+        <v>0.8213842844427718</v>
       </c>
       <c r="Q3">
-        <v>23.20974196317234</v>
+        <v>23.59637749568483</v>
       </c>
       <c r="R3">
-        <v>-90.16844812167656</v>
+        <v>-90.16844812167541</v>
       </c>
       <c r="S3">
-        <v>155.04754652685</v>
+        <v>155.1787942930976</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -11771,22 +11771,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8180647984058403</v>
+        <v>0.8156809317672142</v>
       </c>
       <c r="O4">
-        <v>0.6713200058989205</v>
+        <v>0.6713200058989618</v>
       </c>
       <c r="P4">
-        <v>0.8270854595416767</v>
+        <v>0.8213842844626177</v>
       </c>
       <c r="Q4">
-        <v>23.20974196454116</v>
+        <v>23.59637749700484</v>
       </c>
       <c r="R4">
-        <v>-90.16844812081625</v>
+        <v>-90.16844812081509</v>
       </c>
       <c r="S4">
-        <v>155.0475465263549</v>
+        <v>155.178794292592</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -11833,22 +11833,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.7482250666141222</v>
+        <v>0.7476921982474338</v>
       </c>
       <c r="O5">
-        <v>0.6190173487748427</v>
+        <v>0.6190173487748922</v>
       </c>
       <c r="P5">
-        <v>0.8357185262520522</v>
+        <v>0.829874703098471</v>
       </c>
       <c r="Q5">
-        <v>25.02259488108529</v>
+        <v>25.60808363856681</v>
       </c>
       <c r="R5">
-        <v>-80.28796181488092</v>
+        <v>-80.28796181488039</v>
       </c>
       <c r="S5">
-        <v>159.4275317671639</v>
+        <v>159.7684289631866</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -11895,22 +11895,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8180647984058403</v>
+        <v>0.8156809317672141</v>
       </c>
       <c r="O6">
-        <v>0.6713200058989205</v>
+        <v>0.6713200058989617</v>
       </c>
       <c r="P6">
-        <v>0.8270854595416767</v>
+        <v>0.8213842844626177</v>
       </c>
       <c r="Q6">
-        <v>23.20974196454116</v>
+        <v>23.59637749700483</v>
       </c>
       <c r="R6">
-        <v>-90.16844812081625</v>
+        <v>-90.16844812081509</v>
       </c>
       <c r="S6">
-        <v>155.0475465263549</v>
+        <v>155.178794292592</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -11957,22 +11957,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.8180647983709102</v>
+        <v>0.8156809317346242</v>
       </c>
       <c r="O7">
-        <v>0.6713200059077518</v>
+        <v>0.6713200059077928</v>
       </c>
       <c r="P7">
-        <v>0.8270854595751473</v>
+        <v>0.8213842844970414</v>
       </c>
       <c r="Q7">
-        <v>23.20974196789097</v>
+        <v>23.59637750042545</v>
       </c>
       <c r="R7">
-        <v>-90.16844811247771</v>
+        <v>-90.16844811247655</v>
       </c>
       <c r="S7">
-        <v>155.0475465290439</v>
+        <v>155.1787942954289</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -11986,58 +11986,58 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>29.19696786445927</v>
+        <v>28.88667565645268</v>
       </c>
       <c r="D8">
-        <v>25.26741185818866</v>
+        <v>26.26695217365569</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>6.742751002901383</v>
+        <v>6.671092085905563</v>
       </c>
       <c r="G8">
-        <v>5.83525890217228</v>
+        <v>6.066092853692282</v>
       </c>
       <c r="H8">
-        <v>0.004540640357537321</v>
+        <v>0.003557604122208292</v>
       </c>
       <c r="I8">
-        <v>0.007926334487991512</v>
+        <v>0.007673124089799144</v>
       </c>
       <c r="J8">
-        <v>0.002093407521764378</v>
+        <v>0.002093407521764388</v>
       </c>
       <c r="K8">
-        <v>0.007573622492677809</v>
+        <v>0.00757362249267782</v>
       </c>
       <c r="L8">
-        <v>0.002093407521783539</v>
+        <v>0.002093407521783568</v>
       </c>
       <c r="M8">
-        <v>0.007573622492710656</v>
+        <v>0.007573622492710651</v>
       </c>
       <c r="N8">
-        <v>0.5791090649906225</v>
+        <v>0.5634187549374847</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>0.5791090649908585</v>
+        <v>0.5634187549377596</v>
       </c>
       <c r="Q8">
-        <v>-4.304620283632229</v>
+        <v>-2.985556658200406</v>
       </c>
       <c r="R8">
         <v>0</v>
       </c>
       <c r="S8">
-        <v>175.6953797163158</v>
+        <v>177.0144433417419</v>
       </c>
       <c r="T8">
-        <v>25.35842643462954</v>
+        <v>26.64630061021342</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -12081,22 +12081,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.8180647983709102</v>
+        <v>0.8156809317346242</v>
       </c>
       <c r="O9">
-        <v>0.6713200059077518</v>
+        <v>0.6713200059077928</v>
       </c>
       <c r="P9">
-        <v>0.8270854595751473</v>
+        <v>0.8213842844970414</v>
       </c>
       <c r="Q9">
-        <v>23.20974196789097</v>
+        <v>23.59637750042545</v>
       </c>
       <c r="R9">
-        <v>-90.16844811247771</v>
+        <v>-90.16844811247655</v>
       </c>
       <c r="S9">
-        <v>155.047546529044</v>
+        <v>155.1787942954289</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -12432,22 +12432,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8070572036575052</v>
+        <v>0.8043782236849795</v>
       </c>
       <c r="O2">
-        <v>0.6753383008319636</v>
+        <v>0.6753383008319989</v>
       </c>
       <c r="P2">
-        <v>0.7891306687428484</v>
+        <v>0.7842305382658266</v>
       </c>
       <c r="Q2">
-        <v>23.11067999091066</v>
+        <v>23.40553628518305</v>
       </c>
       <c r="R2">
-        <v>-93.28996606057378</v>
+        <v>-93.2899660605726</v>
       </c>
       <c r="S2">
-        <v>153.0659392340804</v>
+        <v>153.1095271361261</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -12494,22 +12494,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.7750087455665011</v>
+        <v>0.7727503456239442</v>
       </c>
       <c r="O3">
-        <v>0.6359873651065882</v>
+        <v>0.6359873651066272</v>
       </c>
       <c r="P3">
-        <v>0.7835546349387689</v>
+        <v>0.7781535217805052</v>
       </c>
       <c r="Q3">
-        <v>23.20974196317233</v>
+        <v>23.59637749568483</v>
       </c>
       <c r="R3">
-        <v>-90.16844812167656</v>
+        <v>-90.16844812167541</v>
       </c>
       <c r="S3">
-        <v>155.04754652685</v>
+        <v>155.1787942930976</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -12556,22 +12556,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.7750087455788376</v>
+        <v>0.7727503456368904</v>
       </c>
       <c r="O4">
-        <v>0.6359873651421816</v>
+        <v>0.6359873651422207</v>
       </c>
       <c r="P4">
-        <v>0.7835546349567939</v>
+        <v>0.7781535217993067</v>
       </c>
       <c r="Q4">
-        <v>23.20974196454116</v>
+        <v>23.59637749700483</v>
       </c>
       <c r="R4">
-        <v>-90.16844812081624</v>
+        <v>-90.16844812081509</v>
       </c>
       <c r="S4">
-        <v>155.0475465263549</v>
+        <v>155.178794292592</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -12618,22 +12618,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.7088447900670765</v>
+        <v>0.7083399674109366</v>
       </c>
       <c r="O5">
-        <v>0.5864374801365412</v>
+        <v>0.5864374801365883</v>
       </c>
       <c r="P5">
-        <v>0.7917333296210121</v>
+        <v>0.7861970761842827</v>
       </c>
       <c r="Q5">
-        <v>25.02259488108528</v>
+        <v>25.60808363856681</v>
       </c>
       <c r="R5">
-        <v>-80.28796181488092</v>
+        <v>-80.28796181488038</v>
       </c>
       <c r="S5">
-        <v>159.4275317671639</v>
+        <v>159.7684289631866</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -12680,22 +12680,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.7750087455788377</v>
+        <v>0.7727503456368904</v>
       </c>
       <c r="O6">
-        <v>0.6359873651421816</v>
+        <v>0.6359873651422207</v>
       </c>
       <c r="P6">
-        <v>0.7835546349567939</v>
+        <v>0.7781535217993067</v>
       </c>
       <c r="Q6">
-        <v>23.20974196454116</v>
+        <v>23.59637749700483</v>
       </c>
       <c r="R6">
-        <v>-90.16844812081625</v>
+        <v>-90.16844812081509</v>
       </c>
       <c r="S6">
-        <v>155.047546526355</v>
+        <v>155.178794292592</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -12742,22 +12742,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.7750087455457459</v>
+        <v>0.7727503456060156</v>
       </c>
       <c r="O7">
-        <v>0.6359873651505478</v>
+        <v>0.6359873651505867</v>
       </c>
       <c r="P7">
-        <v>0.7835546349885029</v>
+        <v>0.7781535218319187</v>
       </c>
       <c r="Q7">
-        <v>23.20974196789097</v>
+        <v>23.59637750042545</v>
       </c>
       <c r="R7">
-        <v>-90.16844811247771</v>
+        <v>-90.16844811247655</v>
       </c>
       <c r="S7">
-        <v>155.047546529044</v>
+        <v>155.1787942954289</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -12771,58 +12771,58 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>27.66028495962071</v>
+        <v>27.36632392455516</v>
       </c>
       <c r="D8">
-        <v>23.9375477424269</v>
+        <v>24.88448065966663</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>6.387869282106179</v>
+        <v>6.319981888004034</v>
       </c>
       <c r="G8">
-        <v>5.528139935507579</v>
+        <v>5.746824728635386</v>
       </c>
       <c r="H8">
-        <v>0.004540640357537321</v>
+        <v>0.003557604122208292</v>
       </c>
       <c r="I8">
-        <v>0.007926334487991512</v>
+        <v>0.007673124089799144</v>
       </c>
       <c r="J8">
-        <v>0.002093407521764378</v>
+        <v>0.002093407521764388</v>
       </c>
       <c r="K8">
-        <v>0.007573622492677809</v>
+        <v>0.00757362249267782</v>
       </c>
       <c r="L8">
-        <v>0.002093407521783539</v>
+        <v>0.002093407521783568</v>
       </c>
       <c r="M8">
-        <v>0.007573622492710656</v>
+        <v>0.007573622492710651</v>
       </c>
       <c r="N8">
-        <v>0.5486296328681043</v>
+        <v>0.5337651288144869</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>0.5486296328683278</v>
+        <v>0.5337651288147472</v>
       </c>
       <c r="Q8">
-        <v>-4.304620283632235</v>
+        <v>-2.985556658200399</v>
       </c>
       <c r="R8">
         <v>0</v>
       </c>
       <c r="S8">
-        <v>175.6953797163158</v>
+        <v>177.0144433417419</v>
       </c>
       <c r="T8">
-        <v>24.02377207680028</v>
+        <v>25.24386338402638</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -12866,22 +12866,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.7750087455457461</v>
+        <v>0.7727503456060157</v>
       </c>
       <c r="O9">
-        <v>0.6359873651505478</v>
+        <v>0.635987365150587</v>
       </c>
       <c r="P9">
-        <v>0.7835546349885029</v>
+        <v>0.7781535218319187</v>
       </c>
       <c r="Q9">
-        <v>23.20974196789097</v>
+        <v>23.59637750042546</v>
       </c>
       <c r="R9">
-        <v>-90.16844811247772</v>
+        <v>-90.16844811247655</v>
       </c>
       <c r="S9">
-        <v>155.047546529044</v>
+        <v>155.1787942954289</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -13000,22 +13000,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.949945125845628</v>
+        <v>0.9499451189447239</v>
       </c>
       <c r="O2">
         <v>0.9497921483405678</v>
       </c>
       <c r="P2">
-        <v>0.9498470379923126</v>
+        <v>0.949847032210335</v>
       </c>
       <c r="Q2">
-        <v>29.99125751517711</v>
+        <v>29.99125767751679</v>
       </c>
       <c r="R2">
         <v>-90.01024752540668</v>
       </c>
       <c r="S2">
-        <v>149.9984965345466</v>
+        <v>149.9984962552687</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -13062,22 +13062,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9499104965899952</v>
+        <v>0.9499104892448446</v>
       </c>
       <c r="O3">
         <v>0.9497318532872357</v>
       </c>
       <c r="P3">
-        <v>0.9498213805738699</v>
+        <v>0.9498213731324714</v>
       </c>
       <c r="Q3">
-        <v>29.99067571359946</v>
+        <v>29.99067597604334</v>
       </c>
       <c r="R3">
         <v>-90.00931084057518</v>
       </c>
       <c r="S3">
-        <v>150.0000149372788</v>
+        <v>150.0000146848684</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -13124,22 +13124,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9499104965900019</v>
+        <v>0.9499104892448512</v>
       </c>
       <c r="O4">
         <v>0.9497318532872665</v>
       </c>
       <c r="P4">
-        <v>0.9498213805738941</v>
+        <v>0.9498213731324956</v>
       </c>
       <c r="Q4">
-        <v>29.9906757136009</v>
+        <v>29.99067597604478</v>
       </c>
       <c r="R4">
         <v>-90.00931084057336</v>
       </c>
       <c r="S4">
-        <v>150.0000149372792</v>
+        <v>150.0000146848687</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -13186,22 +13186,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9498318348772989</v>
+        <v>0.9498318276077177</v>
       </c>
       <c r="O5">
         <v>0.949614551949966</v>
       </c>
       <c r="P5">
-        <v>0.9497827581395276</v>
+        <v>0.9497827474807838</v>
       </c>
       <c r="Q5">
-        <v>29.9907230122039</v>
+        <v>29.9907235014129</v>
       </c>
       <c r="R5">
         <v>-90.0051288543726</v>
       </c>
       <c r="S5">
-        <v>150.0041483765712</v>
+        <v>150.0041482415535</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -13248,22 +13248,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9499104965900019</v>
+        <v>0.9499104892448512</v>
       </c>
       <c r="O6">
         <v>0.9497318532872665</v>
       </c>
       <c r="P6">
-        <v>0.9498213805738941</v>
+        <v>0.9498213731324956</v>
       </c>
       <c r="Q6">
-        <v>29.9906757136009</v>
+        <v>29.99067597604478</v>
       </c>
       <c r="R6">
         <v>-90.00931084057336</v>
       </c>
       <c r="S6">
-        <v>150.0000149372792</v>
+        <v>150.0000146848687</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -13310,22 +13310,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.9499104965899509</v>
+        <v>0.9499104892448004</v>
       </c>
       <c r="O7">
         <v>0.9497318532872218</v>
       </c>
       <c r="P7">
-        <v>0.9498213805739004</v>
+        <v>0.9498213731325018</v>
       </c>
       <c r="Q7">
-        <v>29.99067571360312</v>
+        <v>29.990675976047</v>
       </c>
       <c r="R7">
-        <v>-90.00931084056737</v>
+        <v>-90.00931084056735</v>
       </c>
       <c r="S7">
-        <v>150.000014937283</v>
+        <v>150.0000146848725</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -13339,58 +13339,58 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0.03099732956814233</v>
+        <v>0.03099731459370446</v>
       </c>
       <c r="D8">
-        <v>0.03099358330190006</v>
+        <v>0.03099487359959816</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>0.007158526734800968</v>
+        <v>0.007158523276602623</v>
       </c>
       <c r="G8">
-        <v>0.007157661571658703</v>
+        <v>0.007157959553152477</v>
       </c>
       <c r="H8">
-        <v>0.004540640357537321</v>
+        <v>0.003557604122208292</v>
       </c>
       <c r="I8">
-        <v>0.007926334487991512</v>
+        <v>0.007673124089799144</v>
       </c>
       <c r="J8">
-        <v>0.002093407521764378</v>
+        <v>0.002093407521764388</v>
       </c>
       <c r="K8">
-        <v>0.007573622492677809</v>
+        <v>0.00757362249267782</v>
       </c>
       <c r="L8">
-        <v>0.002093407521783539</v>
+        <v>0.002093407521783568</v>
       </c>
       <c r="M8">
-        <v>0.007573622492710656</v>
+        <v>0.007573622492710651</v>
       </c>
       <c r="N8">
-        <v>0.9496913067370859</v>
+        <v>0.9496912817987025</v>
       </c>
       <c r="O8">
         <v>0.9490823649281281</v>
       </c>
       <c r="P8">
-        <v>0.9493911708242289</v>
+        <v>0.9493911453574876</v>
       </c>
       <c r="Q8">
-        <v>29.96833912475762</v>
+        <v>29.96834002967356</v>
       </c>
       <c r="R8">
         <v>-90.03136899122694</v>
       </c>
       <c r="S8">
-        <v>150.0003111542433</v>
+        <v>150.0003103043058</v>
       </c>
       <c r="T8">
-        <v>0.03099112345909012</v>
+        <v>0.03099367425319512</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -13434,22 +13434,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.9499104965899509</v>
+        <v>0.9499104892448004</v>
       </c>
       <c r="O9">
         <v>0.9497318532872218</v>
       </c>
       <c r="P9">
-        <v>0.9498213805739004</v>
+        <v>0.9498213731325018</v>
       </c>
       <c r="Q9">
-        <v>29.99067571360312</v>
+        <v>29.990675976047</v>
       </c>
       <c r="R9">
-        <v>-90.00931084056737</v>
+        <v>-90.00931084056735</v>
       </c>
       <c r="S9">
-        <v>150.000014937283</v>
+        <v>150.0000146848725</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -13568,22 +13568,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8999480014113943</v>
+        <v>0.8999479948736958</v>
       </c>
       <c r="O2">
         <v>0.8998030753559895</v>
       </c>
       <c r="P2">
-        <v>0.8998550760779701</v>
+        <v>0.8998550706003072</v>
       </c>
       <c r="Q2">
-        <v>29.99125751517711</v>
+        <v>29.99125767751679</v>
       </c>
       <c r="R2">
         <v>-90.01024752540668</v>
       </c>
       <c r="S2">
-        <v>149.9984965345466</v>
+        <v>149.9984962552687</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -13630,22 +13630,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8999151947486206</v>
+        <v>0.899915187790057</v>
       </c>
       <c r="O3">
-        <v>0.8997459537273135</v>
+        <v>0.8997459537273134</v>
       </c>
       <c r="P3">
-        <v>0.8998307690503107</v>
+        <v>0.899830762000565</v>
       </c>
       <c r="Q3">
-        <v>29.99067571359945</v>
+        <v>29.99067597604334</v>
       </c>
       <c r="R3">
         <v>-90.00931084057518</v>
       </c>
       <c r="S3">
-        <v>150.0000149372788</v>
+        <v>150.0000146848683</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -13692,22 +13692,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8999151947486269</v>
+        <v>0.8999151877900633</v>
       </c>
       <c r="O4">
-        <v>0.8997459537273426</v>
+        <v>0.8997459537273428</v>
       </c>
       <c r="P4">
-        <v>0.8998307690503335</v>
+        <v>0.8998307620005879</v>
       </c>
       <c r="Q4">
-        <v>29.9906757136009</v>
+        <v>29.99067597604479</v>
       </c>
       <c r="R4">
-        <v>-90.00931084057336</v>
+        <v>-90.00931084057335</v>
       </c>
       <c r="S4">
-        <v>150.0000149372792</v>
+        <v>150.0000146848687</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -13754,22 +13754,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8998406731271054</v>
+        <v>0.8998406662401338</v>
       </c>
       <c r="O5">
         <v>0.8996348261461863</v>
       </c>
       <c r="P5">
-        <v>0.8997941793761807</v>
+        <v>0.8997941692784238</v>
       </c>
       <c r="Q5">
-        <v>29.9907230122039</v>
+        <v>29.9907235014129</v>
       </c>
       <c r="R5">
         <v>-90.0051288543726</v>
       </c>
       <c r="S5">
-        <v>150.0041483765712</v>
+        <v>150.0041482415535</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -13816,22 +13816,22 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.8999151947486269</v>
+        <v>0.8999151877900633</v>
       </c>
       <c r="O6">
-        <v>0.8997459537273426</v>
+        <v>0.8997459537273428</v>
       </c>
       <c r="P6">
-        <v>0.8998307690503335</v>
+        <v>0.8998307620005879</v>
       </c>
       <c r="Q6">
-        <v>29.9906757136009</v>
+        <v>29.99067597604479</v>
       </c>
       <c r="R6">
-        <v>-90.00931084057336</v>
+        <v>-90.00931084057335</v>
       </c>
       <c r="S6">
-        <v>150.0000149372792</v>
+        <v>150.0000146848687</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -13878,22 +13878,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.8999151947485787</v>
+        <v>0.8999151877900151</v>
       </c>
       <c r="O7">
         <v>0.8997459537273005</v>
       </c>
       <c r="P7">
-        <v>0.8998307690503397</v>
+        <v>0.8998307620005939</v>
       </c>
       <c r="Q7">
-        <v>29.99067571360312</v>
+        <v>29.990675976047</v>
       </c>
       <c r="R7">
         <v>-90.00931084056737</v>
       </c>
       <c r="S7">
-        <v>150.000014937283</v>
+        <v>150.0000146848725</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -13907,58 +13907,58 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0.02936589076038197</v>
+        <v>0.0293658765740726</v>
       </c>
       <c r="D8">
-        <v>0.02936234166609667</v>
+        <v>0.02936356405337256</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>0.006781762075255998</v>
+        <v>0.006781758799068136</v>
       </c>
       <c r="G8">
-        <v>0.006780942447027386</v>
+        <v>0.006781224745280709</v>
       </c>
       <c r="H8">
-        <v>0.004540640357537321</v>
+        <v>0.003557604122208292</v>
       </c>
       <c r="I8">
-        <v>0.007926334487991512</v>
+        <v>0.007673124089799144</v>
       </c>
       <c r="J8">
-        <v>0.002093407521764378</v>
+        <v>0.002093407521764388</v>
       </c>
       <c r="K8">
-        <v>0.007573622492677809</v>
+        <v>0.00757362249267782</v>
       </c>
       <c r="L8">
-        <v>0.002093407521783539</v>
+        <v>0.002093407521783568</v>
       </c>
       <c r="M8">
-        <v>0.007573622492710656</v>
+        <v>0.007573622492710651</v>
       </c>
       <c r="N8">
-        <v>0.8997075412066544</v>
+        <v>0.899707517580818</v>
       </c>
       <c r="O8">
-        <v>0.8991306489746326</v>
+        <v>0.8991306489746328</v>
       </c>
       <c r="P8">
-        <v>0.8994232019247544</v>
+        <v>0.8994231777983681</v>
       </c>
       <c r="Q8">
-        <v>29.96833912475762</v>
+        <v>29.96834002967356</v>
       </c>
       <c r="R8">
         <v>-90.03136899122694</v>
       </c>
       <c r="S8">
-        <v>150.0003111542433</v>
+        <v>150.0003103043058</v>
       </c>
       <c r="T8">
-        <v>0.02936001128873027</v>
+        <v>0.02936242783048025</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -14002,22 +14002,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.8999151947485787</v>
+        <v>0.8999151877900151</v>
       </c>
       <c r="O9">
         <v>0.8997459537273005</v>
       </c>
       <c r="P9">
-        <v>0.8998307690503397</v>
+        <v>0.8998307620005939</v>
       </c>
       <c r="Q9">
-        <v>29.99067571360312</v>
+        <v>29.990675976047</v>
       </c>
       <c r="R9">
         <v>-90.00931084056737</v>
       </c>
       <c r="S9">
-        <v>150.000014937283</v>
+        <v>150.0000146848725</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -15221,16 +15221,16 @@
         <v>1.003352943349514</v>
       </c>
       <c r="O2">
-        <v>0.7956426181710523</v>
+        <v>0.7956426181710524</v>
       </c>
       <c r="P2">
-        <v>0.9816090407041438</v>
+        <v>0.9816090407041441</v>
       </c>
       <c r="Q2">
-        <v>23.34804219201271</v>
+        <v>23.3480421920127</v>
       </c>
       <c r="R2">
-        <v>-91.70926262351985</v>
+        <v>-91.70926262351981</v>
       </c>
       <c r="S2">
         <v>156.1029588230871</v>
@@ -15277,19 +15277,19 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9850194515443937</v>
+        <v>0.9850194515443935</v>
       </c>
       <c r="O3">
-        <v>0.7558344349760378</v>
+        <v>0.755834434976038</v>
       </c>
       <c r="P3">
-        <v>0.984443688802033</v>
+        <v>0.9844436888020335</v>
       </c>
       <c r="Q3">
-        <v>22.56086167541623</v>
+        <v>22.56086167541624</v>
       </c>
       <c r="R3">
-        <v>-90.0472647664553</v>
+        <v>-90.04726476645526</v>
       </c>
       <c r="S3">
         <v>157.4252155756931</v>
@@ -15336,19 +15336,19 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9850194515436129</v>
+        <v>0.9850194515436125</v>
       </c>
       <c r="O4">
-        <v>0.7558344349967169</v>
+        <v>0.7558344349967171</v>
       </c>
       <c r="P4">
-        <v>0.9844436888107529</v>
+        <v>0.9844436888107531</v>
       </c>
       <c r="Q4">
         <v>22.56086167608663</v>
       </c>
       <c r="R4">
-        <v>-90.0472647656743</v>
+        <v>-90.04726476567426</v>
       </c>
       <c r="S4">
         <v>157.4252155752521</v>
@@ -15395,22 +15395,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9449426229607835</v>
+        <v>0.944942622960783</v>
       </c>
       <c r="O5">
-        <v>0.7084903204199863</v>
+        <v>0.7084903204199864</v>
       </c>
       <c r="P5">
-        <v>1.005888938288717</v>
+        <v>1.005888938288718</v>
       </c>
       <c r="Q5">
         <v>21.91841328792632</v>
       </c>
       <c r="R5">
-        <v>-84.70550824734637</v>
+        <v>-84.70550824734634</v>
       </c>
       <c r="S5">
-        <v>159.471776748441</v>
+        <v>159.4717767484409</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -15454,19 +15454,19 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0.9850194515436129</v>
+        <v>0.9850194515436125</v>
       </c>
       <c r="O6">
-        <v>0.755834434996717</v>
+        <v>0.7558344349967171</v>
       </c>
       <c r="P6">
-        <v>0.9844436888107529</v>
+        <v>0.9844436888107531</v>
       </c>
       <c r="Q6">
         <v>22.56086167608663</v>
       </c>
       <c r="R6">
-        <v>-90.0472647656743</v>
+        <v>-90.04726476567426</v>
       </c>
       <c r="S6">
         <v>157.4252155752521</v>
@@ -15513,19 +15513,19 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.9850194515001651</v>
+        <v>0.9850194515001646</v>
       </c>
       <c r="O7">
-        <v>0.7558344350062859</v>
+        <v>0.7558344350062862</v>
       </c>
       <c r="P7">
-        <v>0.9844436888578996</v>
+        <v>0.9844436888579</v>
       </c>
       <c r="Q7">
-        <v>22.56086167744052</v>
+        <v>22.56086167744051</v>
       </c>
       <c r="R7">
-        <v>-90.04726475823678</v>
+        <v>-90.04726475823675</v>
       </c>
       <c r="S7">
         <v>157.4252155760888</v>
@@ -15554,34 +15554,34 @@
         <v>6.713391731671747</v>
       </c>
       <c r="H8">
-        <v>0.002657050495199304</v>
+        <v>0.002145052455584837</v>
       </c>
       <c r="I8">
-        <v>0.007445544226858886</v>
+        <v>0.007192333827821748</v>
       </c>
       <c r="J8">
-        <v>0.001382566736038376</v>
+        <v>0.001382566736038385</v>
       </c>
       <c r="K8">
-        <v>0.007090446173215316</v>
+        <v>0.007090446173215331</v>
       </c>
       <c r="L8">
-        <v>0.001382566736026977</v>
+        <v>0.001382566736026993</v>
       </c>
       <c r="M8">
         <v>0.007090446173195246</v>
       </c>
       <c r="N8">
-        <v>0.9093266326775831</v>
+        <v>0.909326632677583</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>0.9093266326777132</v>
+        <v>0.9093266326777131</v>
       </c>
       <c r="Q8">
-        <v>-4.410319458857351E-12</v>
+        <v>-4.432602499447072E-12</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -15631,19 +15631,19 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.9850194515001649</v>
+        <v>0.9850194515001646</v>
       </c>
       <c r="O9">
-        <v>0.7558344350062859</v>
+        <v>0.7558344350062862</v>
       </c>
       <c r="P9">
-        <v>0.9844436888578997</v>
+        <v>0.9844436888579</v>
       </c>
       <c r="Q9">
         <v>22.56086167744051</v>
       </c>
       <c r="R9">
-        <v>-90.04726475823678</v>
+        <v>-90.04726475823675</v>
       </c>
       <c r="S9">
         <v>157.4252155760888</v>
